--- a/data/reports/chip_radar_2026-05-11.xlsx
+++ b/data/reports/chip_radar_2026-05-11.xlsx
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14676</v>
@@ -627,12 +627,12 @@
         <v>-9895</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>6380.83</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5">
+        <v>6300.21</v>
+      </c>
+      <c r="L4" s="6">
         <f>F4*(K4-J4)</f>
         <v/>
       </c>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>9942</v>
@@ -1014,10 +1014,10 @@
         <v>6064</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0</v>
+        <v>2259.55</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>2281.12</v>
       </c>
       <c r="L15" s="5">
         <f>F15*(K15-J15)</f>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>6855</v>
@@ -1078,10 +1078,10 @@
         <v>-622</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0</v>
+        <v>535.55</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>537.89</v>
       </c>
       <c r="L17" s="5">
         <f>F17*(K17-J17)</f>
@@ -1127,10 +1127,10 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>5988</v>
@@ -1142,10 +1142,10 @@
         <v>4520</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0</v>
+        <v>1761.18</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
+        <v>1835.25</v>
       </c>
       <c r="L19" s="5">
         <f>F19*(K19-J19)</f>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F24" s="3" t="n">
         <v>0</v>
@@ -1337,7 +1337,7 @@
         <v>1590</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0</v>
+        <v>2304.43</v>
       </c>
       <c r="K24" s="4" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F25" s="3" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
         <v>1572</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0</v>
+        <v>5241.67</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>0</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>1133</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0</v>
+        <v>2309</v>
       </c>
       <c r="K27" s="4" t="n">
         <v>0</v>
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0</v>
@@ -1497,7 +1497,7 @@
         <v>1063</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0</v>
+        <v>5355</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>0</v>
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
@@ -1561,7 +1561,7 @@
         <v>782</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0</v>
+        <v>3934.5</v>
       </c>
       <c r="K31" s="4" t="n">
         <v>0</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>777</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0</v>
+        <v>2601.67</v>
       </c>
       <c r="K32" s="4" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>4209</v>
@@ -2022,12 +2022,12 @@
         <v>2356</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>0</v>
+        <v>3826.36</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="5">
+        <v>3706.4</v>
+      </c>
+      <c r="L44" s="6">
         <f>F44*(K44-J44)</f>
         <v/>
       </c>
@@ -2138,10 +2138,10 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G47" s="3" t="n">
         <v>4369</v>
@@ -2153,10 +2153,10 @@
         <v>3014</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>0</v>
+        <v>2184.45</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>2258.5</v>
       </c>
       <c r="L47" s="5">
         <f>F47*(K47-J47)</f>
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>2802</v>
@@ -2217,10 +2217,10 @@
         <v>2283</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>0</v>
+        <v>4003</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>5191</v>
       </c>
       <c r="L49" s="5">
         <f>F49*(K49-J49)</f>
@@ -2298,10 +2298,10 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="G52" s="3" t="n">
         <v>2416</v>
@@ -2313,12 +2313,12 @@
         <v>-353</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>0</v>
+        <v>215.7</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="5">
+        <v>214.67</v>
+      </c>
+      <c r="L52" s="6">
         <f>F52*(K52-J52)</f>
         <v/>
       </c>
@@ -2362,10 +2362,10 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>2170</v>
@@ -2377,12 +2377,12 @@
         <v>644</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>0</v>
+        <v>394.51</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="5">
+        <v>391.21</v>
+      </c>
+      <c r="L54" s="6">
         <f>F54*(K54-J54)</f>
         <v/>
       </c>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>13802</v>
@@ -2668,10 +2668,10 @@
         <v>12566</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>0</v>
+        <v>5750.83</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>6180.5</v>
       </c>
       <c r="L62" s="5">
         <f>F62*(K62-J62)</f>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>7636</v>
@@ -3055,10 +3055,10 @@
         <v>1250</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>0</v>
+        <v>6362.92</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>6386.3</v>
       </c>
       <c r="L73" s="5">
         <f>F73*(K73-J73)</f>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>5405</v>
@@ -3119,10 +3119,10 @@
         <v>4918</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>0</v>
+        <v>3860.57</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>0</v>
+        <v>4868</v>
       </c>
       <c r="L75" s="5">
         <f>F75*(K75-J75)</f>
@@ -3277,10 +3277,10 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G79" s="3" t="n">
         <v>54376</v>
@@ -3292,12 +3292,12 @@
         <v>52195</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>0</v>
+        <v>5723.84</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" s="5">
+        <v>5453</v>
+      </c>
+      <c r="L79" s="6">
         <f>F79*(K79-J79)</f>
         <v/>
       </c>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>12446</v>
@@ -3452,10 +3452,10 @@
         <v>8127</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>0</v>
+        <v>2222.5</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>2273.37</v>
       </c>
       <c r="L84" s="5">
         <f>F84*(K84-J84)</f>
@@ -3565,10 +3565,10 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>8955</v>
@@ -3580,12 +3580,12 @@
         <v>5803</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>0</v>
+        <v>5267.41</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="5">
+        <v>5253.17</v>
+      </c>
+      <c r="L88" s="6">
         <f>F88*(K88-J88)</f>
         <v/>
       </c>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>3376</v>
@@ -3711,10 +3711,10 @@
         <v>-5434</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>0</v>
+        <v>5626</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>5873.47</v>
       </c>
       <c r="L91" s="5">
         <f>F91*(K91-J91)</f>
@@ -3760,10 +3760,10 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>3003</v>
@@ -3775,12 +3775,12 @@
         <v>-4604</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>0</v>
+        <v>2309.77</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" s="5">
+        <v>2237.26</v>
+      </c>
+      <c r="L93" s="6">
         <f>F93*(K93-J93)</f>
         <v/>
       </c>
@@ -3792,10 +3792,10 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G94" s="3" t="n">
         <v>1935</v>
@@ -3807,10 +3807,10 @@
         <v>374</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>0</v>
+        <v>3870.2</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>3903.5</v>
       </c>
       <c r="L94" s="5">
         <f>F94*(K94-J94)</f>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>1875</v>
@@ -3839,10 +3839,10 @@
         <v>1675</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>0</v>
+        <v>852.23</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>1001.5</v>
       </c>
       <c r="L95" s="5">
         <f>F95*(K95-J95)</f>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>1798</v>
@@ -3871,12 +3871,12 @@
         <v>490</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>0</v>
+        <v>243.01</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="5">
+        <v>242.3</v>
+      </c>
+      <c r="L96" s="6">
         <f>F96*(K96-J96)</f>
         <v/>
       </c>
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F97" s="3" t="n">
         <v>0</v>
@@ -3903,7 +3903,7 @@
         <v>1620</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>0</v>
+        <v>5443.67</v>
       </c>
       <c r="K97" s="4" t="n">
         <v>0</v>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>1231</v>
@@ -3967,10 +3967,10 @@
         <v>452</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>0</v>
+        <v>1538.75</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
+        <v>1557.6</v>
       </c>
       <c r="L99" s="5">
         <f>F99*(K99-J99)</f>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>0</v>
+        <v>1101</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>33149</v>
@@ -4098,10 +4098,10 @@
         <v>-2621</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>0</v>
+        <v>301.08</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>301.09</v>
       </c>
       <c r="L102" s="5">
         <f>F102*(K102-J102)</f>
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G105" s="3" t="n">
         <v>10744</v>
@@ -4194,12 +4194,12 @@
         <v>9349</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>0</v>
+        <v>1821.1</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="5">
+        <v>1743.75</v>
+      </c>
+      <c r="L105" s="6">
         <f>F105*(K105-J105)</f>
         <v/>
       </c>
@@ -4211,10 +4211,10 @@
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>8283</v>
@@ -4226,12 +4226,12 @@
         <v>2046</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>0</v>
+        <v>462.72</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="5">
+        <v>462</v>
+      </c>
+      <c r="L106" s="6">
         <f>F106*(K106-J106)</f>
         <v/>
       </c>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G107" s="3" t="n">
         <v>7556</v>
@@ -4258,12 +4258,12 @@
         <v>3338</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>0</v>
+        <v>3976.58</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="5">
+        <v>3835</v>
+      </c>
+      <c r="L107" s="6">
         <f>F107*(K107-J107)</f>
         <v/>
       </c>
@@ -4307,10 +4307,10 @@
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G109" s="3" t="n">
         <v>6626</v>
@@ -4322,10 +4322,10 @@
         <v>-3693</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>0</v>
+        <v>3897.88</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>3968.81</v>
       </c>
       <c r="L109" s="5">
         <f>F109*(K109-J109)</f>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>6278</v>
@@ -4354,12 +4354,12 @@
         <v>1519</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>0</v>
+        <v>1184.62</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="5">
+        <v>1160.73</v>
+      </c>
+      <c r="L110" s="6">
         <f>F110*(K110-J110)</f>
         <v/>
       </c>
@@ -4598,10 +4598,10 @@
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>2182</v>
@@ -4613,12 +4613,12 @@
         <v>1588</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>0</v>
+        <v>3637.33</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="5">
+        <v>2967.5</v>
+      </c>
+      <c r="L117" s="6">
         <f>F117*(K117-J117)</f>
         <v/>
       </c>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>1324</v>
@@ -4645,12 +4645,12 @@
         <v>315</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>0</v>
+        <v>426.94</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="5">
+        <v>420.5</v>
+      </c>
+      <c r="L118" s="6">
         <f>F118*(K118-J118)</f>
         <v/>
       </c>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G123" s="3" t="n">
         <v>8137</v>
@@ -4840,10 +4840,10 @@
         <v>7152</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>0</v>
+        <v>2260.17</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>2463</v>
       </c>
       <c r="L123" s="5">
         <f>F123*(K123-J123)</f>
@@ -4921,10 +4921,10 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G126" s="3" t="n">
         <v>4250</v>
@@ -4936,12 +4936,12 @@
         <v>3483</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>0</v>
+        <v>3863.91</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="5">
+        <v>3835</v>
+      </c>
+      <c r="L126" s="6">
         <f>F126*(K126-J126)</f>
         <v/>
       </c>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="E128" s="3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>2890</v>
@@ -5000,10 +5000,10 @@
         <v>-1367</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>0</v>
+        <v>412.93</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>413.26</v>
       </c>
       <c r="L128" s="5">
         <f>F128*(K128-J128)</f>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G129" s="3" t="n">
         <v>2710</v>
@@ -5032,10 +5032,10 @@
         <v>408</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>0</v>
+        <v>4517.33</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>4604.4</v>
       </c>
       <c r="L129" s="5">
         <f>F129*(K129-J129)</f>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G130" s="3" t="n">
         <v>2595</v>
@@ -5064,10 +5064,10 @@
         <v>2018</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>0</v>
+        <v>2595.3</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>2885</v>
       </c>
       <c r="L130" s="5">
         <f>F130*(K130-J130)</f>
@@ -5113,10 +5113,10 @@
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>2472</v>
@@ -5128,12 +5128,12 @@
         <v>1238</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>0</v>
+        <v>6180</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="5">
+        <v>6172</v>
+      </c>
+      <c r="L132" s="6">
         <f>F132*(K132-J132)</f>
         <v/>
       </c>
@@ -5308,10 +5308,10 @@
         </is>
       </c>
       <c r="E137" s="3" t="n">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G137" s="3" t="n">
         <v>35424</v>
@@ -5323,10 +5323,10 @@
         <v>21611</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>0</v>
+        <v>2585.69</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>2606.28</v>
       </c>
       <c r="L137" s="5">
         <f>F137*(K137-J137)</f>
@@ -5372,10 +5372,10 @@
         </is>
       </c>
       <c r="E139" s="3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="G139" s="3" t="n">
         <v>26807</v>
@@ -5387,12 +5387,12 @@
         <v>-41768</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>0</v>
+        <v>2233.91</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" s="5">
+        <v>2233.72</v>
+      </c>
+      <c r="L139" s="6">
         <f>F139*(K139-J139)</f>
         <v/>
       </c>
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="E141" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>24789</v>
@@ -5451,10 +5451,10 @@
         <v>24232</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>0</v>
+        <v>5388.85</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>5566</v>
       </c>
       <c r="L141" s="5">
         <f>F141*(K141-J141)</f>
@@ -5500,10 +5500,10 @@
         </is>
       </c>
       <c r="E143" s="3" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G143" s="3" t="n">
         <v>21815</v>
@@ -5515,10 +5515,10 @@
         <v>18464</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>0</v>
+        <v>5453.65</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
+        <v>5585.17</v>
       </c>
       <c r="L143" s="5">
         <f>F143*(K143-J143)</f>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="E150" s="3" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>46181</v>
@@ -5784,12 +5784,12 @@
         <v>43669</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>0</v>
+        <v>6414.08</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="5">
+        <v>6279</v>
+      </c>
+      <c r="L150" s="6">
         <f>F150*(K150-J150)</f>
         <v/>
       </c>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="E151" s="3" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>44810</v>
@@ -5816,10 +5816,10 @@
         <v>41265</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>0</v>
+        <v>2836.04</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>2953.92</v>
       </c>
       <c r="L151" s="5">
         <f>F151*(K151-J151)</f>
@@ -6092,10 +6092,10 @@
         </is>
       </c>
       <c r="E159" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G159" s="3" t="n">
         <v>14722</v>
@@ -6107,10 +6107,10 @@
         <v>6726</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>0</v>
+        <v>4907.2</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>0</v>
+        <v>4997.56</v>
       </c>
       <c r="L159" s="5">
         <f>F159*(K159-J159)</f>
@@ -6124,10 +6124,10 @@
         </is>
       </c>
       <c r="E160" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G160" s="3" t="n">
         <v>12663</v>
@@ -6139,10 +6139,10 @@
         <v>10907</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>0</v>
+        <v>5756.05</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>0</v>
+        <v>5852.67</v>
       </c>
       <c r="L160" s="5">
         <f>F160*(K160-J160)</f>
@@ -6156,10 +6156,10 @@
         </is>
       </c>
       <c r="E161" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G161" s="3" t="n">
         <v>12332</v>
@@ -6171,12 +6171,12 @@
         <v>10938</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>0</v>
+        <v>5361.7</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L161" s="5">
+        <v>4648.33</v>
+      </c>
+      <c r="L161" s="6">
         <f>F161*(K161-J161)</f>
         <v/>
       </c>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="E172" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G172" s="3" t="n">
         <v>7636</v>
@@ -6558,10 +6558,10 @@
         <v>1250</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>0</v>
+        <v>6362.92</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
+        <v>6386.3</v>
       </c>
       <c r="L172" s="5">
         <f>F172*(K172-J172)</f>
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="E174" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" s="3" t="n">
         <v>5405</v>
@@ -6622,10 +6622,10 @@
         <v>4918</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>0</v>
+        <v>3860.57</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>0</v>
+        <v>4868</v>
       </c>
       <c r="L174" s="5">
         <f>F174*(K174-J174)</f>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="E184" s="3" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G184" s="3" t="n">
         <v>5811</v>
@@ -6977,12 +6977,12 @@
         <v>1435</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>0</v>
+        <v>251.58</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L184" s="5">
+        <v>251.52</v>
+      </c>
+      <c r="L184" s="6">
         <f>F184*(K184-J184)</f>
         <v/>
       </c>
@@ -7189,10 +7189,10 @@
         </is>
       </c>
       <c r="E190" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G190" s="3" t="n">
         <v>11130</v>
@@ -7204,12 +7204,12 @@
         <v>8896</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>0</v>
+        <v>5857.84</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" s="5">
+        <v>5586.25</v>
+      </c>
+      <c r="L190" s="6">
         <f>F190*(K190-J190)</f>
         <v/>
       </c>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="E192" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F192" s="3" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>6391</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>0</v>
+        <v>6392.9</v>
       </c>
       <c r="K192" s="4" t="n">
         <v>0</v>
@@ -7285,10 +7285,10 @@
         </is>
       </c>
       <c r="E193" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G193" s="3" t="n">
         <v>5840</v>
@@ -7300,10 +7300,10 @@
         <v>2058</v>
       </c>
       <c r="J193" s="4" t="n">
-        <v>0</v>
+        <v>5309</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
+        <v>5402.86</v>
       </c>
       <c r="L193" s="5">
         <f>F193*(K193-J193)</f>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="E198" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G198" s="3" t="n">
         <v>2574</v>
@@ -7460,10 +7460,10 @@
         <v>1885</v>
       </c>
       <c r="J198" s="4" t="n">
-        <v>0</v>
+        <v>677.39</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>0</v>
+        <v>689.3</v>
       </c>
       <c r="L198" s="5">
         <f>F198*(K198-J198)</f>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="E204" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G204" s="3" t="n">
         <v>5681</v>
@@ -7697,10 +7697,10 @@
         <v>4604</v>
       </c>
       <c r="J204" s="4" t="n">
-        <v>0</v>
+        <v>5164.55</v>
       </c>
       <c r="K204" s="4" t="n">
-        <v>0</v>
+        <v>5384.5</v>
       </c>
       <c r="L204" s="5">
         <f>F204*(K204-J204)</f>
@@ -7746,10 +7746,10 @@
         </is>
       </c>
       <c r="E206" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G206" s="3" t="n">
         <v>3471</v>
@@ -7761,10 +7761,10 @@
         <v>3193</v>
       </c>
       <c r="J206" s="4" t="n">
-        <v>0</v>
+        <v>2670</v>
       </c>
       <c r="K206" s="4" t="n">
-        <v>0</v>
+        <v>2782</v>
       </c>
       <c r="L206" s="5">
         <f>F206*(K206-J206)</f>
@@ -7778,10 +7778,10 @@
         </is>
       </c>
       <c r="E207" s="3" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="G207" s="3" t="n">
         <v>1980</v>
@@ -7793,10 +7793,10 @@
         <v>279</v>
       </c>
       <c r="J207" s="4" t="n">
-        <v>0</v>
+        <v>241.52</v>
       </c>
       <c r="K207" s="4" t="n">
-        <v>0</v>
+        <v>242.97</v>
       </c>
       <c r="L207" s="5">
         <f>F207*(K207-J207)</f>
@@ -8005,10 +8005,10 @@
         </is>
       </c>
       <c r="E213" s="3" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G213" s="3" t="n">
         <v>15547</v>
@@ -8020,12 +8020,12 @@
         <v>2060</v>
       </c>
       <c r="J213" s="4" t="n">
-        <v>0</v>
+        <v>673.04</v>
       </c>
       <c r="K213" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L213" s="5">
+        <v>671</v>
+      </c>
+      <c r="L213" s="6">
         <f>F213*(K213-J213)</f>
         <v/>
       </c>
@@ -8037,10 +8037,10 @@
         </is>
       </c>
       <c r="E214" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G214" s="3" t="n">
         <v>14003</v>
@@ -8052,10 +8052,10 @@
         <v>13126</v>
       </c>
       <c r="J214" s="4" t="n">
-        <v>0</v>
+        <v>2857.71</v>
       </c>
       <c r="K214" s="4" t="n">
-        <v>0</v>
+        <v>2924.67</v>
       </c>
       <c r="L214" s="5">
         <f>F214*(K214-J214)</f>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="E215" s="3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F215" s="3" t="n">
         <v>0</v>
@@ -8084,7 +8084,7 @@
         <v>13902</v>
       </c>
       <c r="J215" s="4" t="n">
-        <v>0</v>
+        <v>2254.11</v>
       </c>
       <c r="K215" s="4" t="n">
         <v>0</v>
@@ -8197,10 +8197,10 @@
         </is>
       </c>
       <c r="E219" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G219" s="3" t="n">
         <v>8891</v>
@@ -8212,12 +8212,12 @@
         <v>1443</v>
       </c>
       <c r="J219" s="4" t="n">
-        <v>0</v>
+        <v>4041.36</v>
       </c>
       <c r="K219" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L219" s="5">
+        <v>3920.26</v>
+      </c>
+      <c r="L219" s="6">
         <f>F219*(K219-J219)</f>
         <v/>
       </c>
@@ -8229,10 +8229,10 @@
         </is>
       </c>
       <c r="E220" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G220" s="3" t="n">
         <v>8756</v>
@@ -8244,10 +8244,10 @@
         <v>8221</v>
       </c>
       <c r="J220" s="4" t="n">
-        <v>0</v>
+        <v>2575.26</v>
       </c>
       <c r="K220" s="4" t="n">
-        <v>0</v>
+        <v>2675.5</v>
       </c>
       <c r="L220" s="5">
         <f>F220*(K220-J220)</f>
@@ -8392,10 +8392,10 @@
         </is>
       </c>
       <c r="E224" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G224" s="3" t="n">
         <v>4850</v>
@@ -8407,10 +8407,10 @@
         <v>4053</v>
       </c>
       <c r="J224" s="4" t="n">
-        <v>0</v>
+        <v>1310.7</v>
       </c>
       <c r="K224" s="4" t="n">
-        <v>0</v>
+        <v>1328.67</v>
       </c>
       <c r="L224" s="5">
         <f>F224*(K224-J224)</f>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="E225" s="3" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G225" s="3" t="n">
         <v>4581</v>
@@ -8439,12 +8439,12 @@
         <v>989</v>
       </c>
       <c r="J225" s="4" t="n">
-        <v>0</v>
+        <v>234.92</v>
       </c>
       <c r="K225" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L225" s="5">
+        <v>234.77</v>
+      </c>
+      <c r="L225" s="6">
         <f>F225*(K225-J225)</f>
         <v/>
       </c>
@@ -8456,10 +8456,10 @@
         </is>
       </c>
       <c r="E226" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G226" s="3" t="n">
         <v>4417</v>
@@ -8471,10 +8471,10 @@
         <v>3873</v>
       </c>
       <c r="J226" s="4" t="n">
-        <v>0</v>
+        <v>2208.6</v>
       </c>
       <c r="K226" s="4" t="n">
-        <v>0</v>
+        <v>2718.5</v>
       </c>
       <c r="L226" s="5">
         <f>F226*(K226-J226)</f>
@@ -8488,10 +8488,10 @@
         </is>
       </c>
       <c r="E227" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G227" s="3" t="n">
         <v>3749</v>
@@ -8503,12 +8503,12 @@
         <v>1947</v>
       </c>
       <c r="J227" s="4" t="n">
-        <v>0</v>
+        <v>3749.1</v>
       </c>
       <c r="K227" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L227" s="5">
+        <v>3603.8</v>
+      </c>
+      <c r="L227" s="6">
         <f>F227*(K227-J227)</f>
         <v/>
       </c>
@@ -8715,10 +8715,10 @@
         </is>
       </c>
       <c r="E233" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G233" s="3" t="n">
         <v>4132</v>
@@ -8730,12 +8730,12 @@
         <v>-1501</v>
       </c>
       <c r="J233" s="4" t="n">
-        <v>0</v>
+        <v>2582.81</v>
       </c>
       <c r="K233" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L233" s="5">
+        <v>2560.59</v>
+      </c>
+      <c r="L233" s="6">
         <f>F233*(K233-J233)</f>
         <v/>
       </c>
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="E236" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F236" s="3" t="n">
         <v>0</v>
@@ -8826,7 +8826,7 @@
         <v>2780</v>
       </c>
       <c r="J236" s="4" t="n">
-        <v>0</v>
+        <v>2826.4</v>
       </c>
       <c r="K236" s="4" t="n">
         <v>0</v>
@@ -8843,10 +8843,10 @@
         </is>
       </c>
       <c r="E237" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G237" s="3" t="n">
         <v>2322</v>
@@ -8858,10 +8858,10 @@
         <v>-533</v>
       </c>
       <c r="J237" s="4" t="n">
-        <v>0</v>
+        <v>2579.67</v>
       </c>
       <c r="K237" s="4" t="n">
-        <v>0</v>
+        <v>2595.18</v>
       </c>
       <c r="L237" s="5">
         <f>F237*(K237-J237)</f>
@@ -8875,10 +8875,10 @@
         </is>
       </c>
       <c r="E238" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G238" s="3" t="n">
         <v>2315</v>
@@ -8890,12 +8890,12 @@
         <v>1259</v>
       </c>
       <c r="J238" s="4" t="n">
-        <v>0</v>
+        <v>3857.83</v>
       </c>
       <c r="K238" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L238" s="5">
+        <v>3521.67</v>
+      </c>
+      <c r="L238" s="6">
         <f>F238*(K238-J238)</f>
         <v/>
       </c>
@@ -8907,10 +8907,10 @@
         </is>
       </c>
       <c r="E239" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G239" s="3" t="n">
         <v>2156</v>
@@ -8922,12 +8922,12 @@
         <v>-185</v>
       </c>
       <c r="J239" s="4" t="n">
-        <v>0</v>
+        <v>4311.6</v>
       </c>
       <c r="K239" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L239" s="5">
+        <v>3901.83</v>
+      </c>
+      <c r="L239" s="6">
         <f>F239*(K239-J239)</f>
         <v/>
       </c>
@@ -8971,10 +8971,10 @@
         </is>
       </c>
       <c r="E241" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G241" s="3" t="n">
         <v>2093</v>
@@ -8986,10 +8986,10 @@
         <v>-542</v>
       </c>
       <c r="J241" s="4" t="n">
-        <v>0</v>
+        <v>5231.75</v>
       </c>
       <c r="K241" s="4" t="n">
-        <v>0</v>
+        <v>5270</v>
       </c>
       <c r="L241" s="5">
         <f>F241*(K241-J241)</f>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="E242" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
         <v>2029</v>
@@ -9018,12 +9018,12 @@
         <v>1599</v>
       </c>
       <c r="J242" s="4" t="n">
-        <v>0</v>
+        <v>2254</v>
       </c>
       <c r="K242" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L242" s="5">
+        <v>2148.5</v>
+      </c>
+      <c r="L242" s="6">
         <f>F242*(K242-J242)</f>
         <v/>
       </c>
@@ -9108,31 +9108,31 @@
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>奇鈦科(3430)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E244" s="3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="G244" s="3" t="n">
-        <v>83</v>
+        <v>915</v>
       </c>
       <c r="H244" s="3" t="n">
-        <v>1805</v>
+        <v>1226</v>
       </c>
       <c r="I244" s="3" t="n">
-        <v>-1722</v>
+        <v>-311</v>
       </c>
       <c r="J244" s="4" t="n">
-        <v>166.4</v>
+        <v>508.11</v>
       </c>
       <c r="K244" s="4" t="n">
-        <v>164.13</v>
-      </c>
-      <c r="L244" s="6">
+        <v>510.71</v>
+      </c>
+      <c r="L244" s="5">
         <f>F244*(K244-J244)</f>
         <v/>
       </c>
@@ -9140,31 +9140,31 @@
     <row r="245" ht="16.5" customHeight="1">
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E245" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>0</v>
+        <v>302</v>
       </c>
       <c r="G245" s="3" t="n">
-        <v>32</v>
+        <v>428</v>
       </c>
       <c r="H245" s="3" t="n">
-        <v>311</v>
+        <v>9021</v>
       </c>
       <c r="I245" s="3" t="n">
-        <v>-279</v>
+        <v>-8593</v>
       </c>
       <c r="J245" s="4" t="n">
-        <v>0</v>
+        <v>305.71</v>
       </c>
       <c r="K245" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L245" s="5">
+        <v>298.71</v>
+      </c>
+      <c r="L245" s="6">
         <f>F245*(K245-J245)</f>
         <v/>
       </c>
@@ -9172,31 +9172,31 @@
     <row r="246" ht="16.5" customHeight="1">
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>健策(3653)</t>
         </is>
       </c>
       <c r="E246" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="H246" s="3" t="n">
-        <v>567</v>
+        <v>3073</v>
       </c>
       <c r="I246" s="3" t="n">
-        <v>-567</v>
+        <v>-2674</v>
       </c>
       <c r="J246" s="4" t="n">
-        <v>0</v>
+        <v>3990</v>
       </c>
       <c r="K246" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L246" s="5">
+        <v>3841.12</v>
+      </c>
+      <c r="L246" s="6">
         <f>F246*(K246-J246)</f>
         <v/>
       </c>
@@ -9204,29 +9204,29 @@
     <row r="247" ht="16.5" customHeight="1">
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E247" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G247" s="3" t="n">
-        <v>0</v>
+        <v>394</v>
       </c>
       <c r="H247" s="3" t="n">
-        <v>1070</v>
+        <v>717</v>
       </c>
       <c r="I247" s="3" t="n">
-        <v>-1070</v>
+        <v>-323</v>
       </c>
       <c r="J247" s="4" t="n">
-        <v>0</v>
+        <v>218.83</v>
       </c>
       <c r="K247" s="4" t="n">
-        <v>0</v>
+        <v>224.06</v>
       </c>
       <c r="L247" s="5">
         <f>F247*(K247-J247)</f>
@@ -9236,89 +9236,194 @@
     <row r="248" ht="16.5" customHeight="1">
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>昶昕(8438)</t>
         </is>
       </c>
       <c r="E248" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>0</v>
+        <v>336</v>
       </c>
       <c r="H248" s="3" t="n">
-        <v>564</v>
+        <v>39</v>
       </c>
       <c r="I248" s="3" t="n">
-        <v>-564</v>
+        <v>297</v>
       </c>
       <c r="J248" s="4" t="n">
-        <v>0</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="K248" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L248" s="5">
+        <v>98</v>
+      </c>
+      <c r="L248" s="6">
         <f>F248*(K248-J248)</f>
         <v/>
       </c>
     </row>
     <row r="249" ht="16.5" customHeight="1">
-      <c r="D249" s="2" t="n"/>
-      <c r="E249" s="3" t="n"/>
-      <c r="F249" s="3" t="n"/>
-      <c r="G249" s="3" t="n"/>
-      <c r="H249" s="3" t="n"/>
-      <c r="I249" s="3" t="n"/>
-      <c r="J249" s="4" t="n"/>
-      <c r="K249" s="4" t="n"/>
-      <c r="L249" s="5" t="n"/>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>辛耘(3583)</t>
+        </is>
+      </c>
+      <c r="E249" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G249" s="3" t="n">
+        <v>209</v>
+      </c>
+      <c r="H249" s="3" t="n">
+        <v>935</v>
+      </c>
+      <c r="I249" s="3" t="n">
+        <v>-726</v>
+      </c>
+      <c r="J249" s="4" t="n">
+        <v>1043.5</v>
+      </c>
+      <c r="K249" s="4" t="n">
+        <v>849.91</v>
+      </c>
+      <c r="L249" s="6">
+        <f>F249*(K249-J249)</f>
+        <v/>
+      </c>
     </row>
     <row r="250" ht="16.5" customHeight="1">
-      <c r="D250" s="2" t="n"/>
-      <c r="E250" s="3" t="n"/>
-      <c r="F250" s="3" t="n"/>
-      <c r="G250" s="3" t="n"/>
-      <c r="H250" s="3" t="n"/>
-      <c r="I250" s="3" t="n"/>
-      <c r="J250" s="4" t="n"/>
-      <c r="K250" s="4" t="n"/>
-      <c r="L250" s="5" t="n"/>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>華邦電(2344)</t>
+        </is>
+      </c>
+      <c r="E250" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>103</v>
+      </c>
+      <c r="G250" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="H250" s="3" t="n">
+        <v>1207</v>
+      </c>
+      <c r="I250" s="3" t="n">
+        <v>-1115</v>
+      </c>
+      <c r="J250" s="4" t="n">
+        <v>115.12</v>
+      </c>
+      <c r="K250" s="4" t="n">
+        <v>117.17</v>
+      </c>
+      <c r="L250" s="5">
+        <f>F250*(K250-J250)</f>
+        <v/>
+      </c>
     </row>
     <row r="251" ht="16.5" customHeight="1">
-      <c r="D251" s="2" t="n"/>
-      <c r="E251" s="3" t="n"/>
-      <c r="F251" s="3" t="n"/>
-      <c r="G251" s="3" t="n"/>
-      <c r="H251" s="3" t="n"/>
-      <c r="I251" s="3" t="n"/>
-      <c r="J251" s="4" t="n"/>
-      <c r="K251" s="4" t="n"/>
-      <c r="L251" s="5" t="n"/>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>奇鈦科(3430)</t>
+        </is>
+      </c>
+      <c r="E251" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="G251" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="H251" s="3" t="n">
+        <v>1805</v>
+      </c>
+      <c r="I251" s="3" t="n">
+        <v>-1722</v>
+      </c>
+      <c r="J251" s="4" t="n">
+        <v>166.4</v>
+      </c>
+      <c r="K251" s="4" t="n">
+        <v>164.13</v>
+      </c>
+      <c r="L251" s="6">
+        <f>F251*(K251-J251)</f>
+        <v/>
+      </c>
     </row>
     <row r="252" ht="16.5" customHeight="1">
-      <c r="D252" s="2" t="n"/>
-      <c r="E252" s="3" t="n"/>
-      <c r="F252" s="3" t="n"/>
-      <c r="G252" s="3" t="n"/>
-      <c r="H252" s="3" t="n"/>
-      <c r="I252" s="3" t="n"/>
-      <c r="J252" s="4" t="n"/>
-      <c r="K252" s="4" t="n"/>
-      <c r="L252" s="5" t="n"/>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>群創(3481)</t>
+        </is>
+      </c>
+      <c r="E252" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>341</v>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="H252" s="3" t="n">
+        <v>1098</v>
+      </c>
+      <c r="I252" s="3" t="n">
+        <v>-1016</v>
+      </c>
+      <c r="J252" s="4" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="K252" s="4" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="L252" s="5">
+        <f>F252*(K252-J252)</f>
+        <v/>
+      </c>
     </row>
     <row r="253" ht="16.5" customHeight="1">
-      <c r="D253" s="2" t="n"/>
-      <c r="E253" s="3" t="n"/>
-      <c r="F253" s="3" t="n"/>
-      <c r="G253" s="3" t="n"/>
-      <c r="H253" s="3" t="n"/>
-      <c r="I253" s="3" t="n"/>
-      <c r="J253" s="4" t="n"/>
-      <c r="K253" s="4" t="n"/>
-      <c r="L253" s="5" t="n"/>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>康舒(6282)</t>
+        </is>
+      </c>
+      <c r="E253" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="G253" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="H253" s="3" t="n">
+        <v>817</v>
+      </c>
+      <c r="I253" s="3" t="n">
+        <v>-749</v>
+      </c>
+      <c r="J253" s="4" t="n">
+        <v>52.54</v>
+      </c>
+      <c r="K253" s="4" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="L253" s="5">
+        <f>F253*(K253-J253)</f>
+        <v/>
+      </c>
     </row>
     <row r="254" ht="16.5" customHeight="1">
       <c r="B254" s="1" t="inlineStr">
@@ -9390,31 +9495,31 @@
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E255" s="3" t="n">
-        <v>2622</v>
+        <v>30730</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>69330</v>
+        <v>360984</v>
       </c>
       <c r="H255" s="3" t="n">
-        <v>2909</v>
+        <v>2439</v>
       </c>
       <c r="I255" s="3" t="n">
-        <v>66421</v>
+        <v>358545</v>
       </c>
       <c r="J255" s="4" t="n">
-        <v>264.42</v>
+        <v>117.47</v>
       </c>
       <c r="K255" s="4" t="n">
-        <v>264.44</v>
-      </c>
-      <c r="L255" s="5">
+        <v>115.05</v>
+      </c>
+      <c r="L255" s="6">
         <f>F255*(K255-J255)</f>
         <v/>
       </c>
@@ -9422,29 +9527,29 @@
     <row r="256" ht="16.5" customHeight="1">
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E256" s="3" t="n">
-        <v>0</v>
+        <v>101621</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="G256" s="3" t="n">
-        <v>31003</v>
+        <v>328208</v>
       </c>
       <c r="H256" s="3" t="n">
-        <v>1636</v>
+        <v>1773</v>
       </c>
       <c r="I256" s="3" t="n">
-        <v>29367</v>
+        <v>326435</v>
       </c>
       <c r="J256" s="4" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="K256" s="4" t="n">
-        <v>0</v>
+        <v>32.3</v>
       </c>
       <c r="L256" s="5">
         <f>F256*(K256-J256)</f>
@@ -9454,29 +9559,29 @@
     <row r="257" ht="16.5" customHeight="1">
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E257" s="3" t="n">
-        <v>0</v>
+        <v>2622</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G257" s="3" t="n">
-        <v>28492</v>
+        <v>69330</v>
       </c>
       <c r="H257" s="3" t="n">
-        <v>11444</v>
+        <v>2909</v>
       </c>
       <c r="I257" s="3" t="n">
-        <v>17048</v>
+        <v>66421</v>
       </c>
       <c r="J257" s="4" t="n">
-        <v>0</v>
+        <v>264.42</v>
       </c>
       <c r="K257" s="4" t="n">
-        <v>0</v>
+        <v>264.44</v>
       </c>
       <c r="L257" s="5">
         <f>F257*(K257-J257)</f>
@@ -9486,31 +9591,31 @@
     <row r="258" ht="16.5" customHeight="1">
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>創意(3443)</t>
         </is>
       </c>
       <c r="E258" s="3" t="n">
-        <v>1782</v>
+        <v>64</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>336</v>
+        <v>40</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>27885</v>
+        <v>36820</v>
       </c>
       <c r="H258" s="3" t="n">
-        <v>5400</v>
+        <v>22808</v>
       </c>
       <c r="I258" s="3" t="n">
-        <v>22485</v>
+        <v>14012</v>
       </c>
       <c r="J258" s="4" t="n">
-        <v>156.48</v>
+        <v>5753.09</v>
       </c>
       <c r="K258" s="4" t="n">
-        <v>160.73</v>
-      </c>
-      <c r="L258" s="5">
+        <v>5701.88</v>
+      </c>
+      <c r="L258" s="6">
         <f>F258*(K258-J258)</f>
         <v/>
       </c>
@@ -9518,29 +9623,29 @@
     <row r="259" ht="16.5" customHeight="1">
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>昇達科(3491)</t>
         </is>
       </c>
       <c r="E259" s="3" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>25941</v>
+        <v>28492</v>
       </c>
       <c r="H259" s="3" t="n">
-        <v>17216</v>
+        <v>11444</v>
       </c>
       <c r="I259" s="3" t="n">
-        <v>8725</v>
+        <v>17048</v>
       </c>
       <c r="J259" s="4" t="n">
-        <v>0</v>
+        <v>1814.78</v>
       </c>
       <c r="K259" s="4" t="n">
-        <v>0</v>
+        <v>1816.59</v>
       </c>
       <c r="L259" s="5">
         <f>F259*(K259-J259)</f>
@@ -9550,31 +9655,31 @@
     <row r="260" ht="16.5" customHeight="1">
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>中美晶(5483)</t>
         </is>
       </c>
       <c r="E260" s="3" t="n">
-        <v>505</v>
+        <v>1782</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>121</v>
+        <v>336</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>17181</v>
+        <v>27885</v>
       </c>
       <c r="H260" s="3" t="n">
-        <v>4020</v>
+        <v>5400</v>
       </c>
       <c r="I260" s="3" t="n">
-        <v>13161</v>
+        <v>22485</v>
       </c>
       <c r="J260" s="4" t="n">
-        <v>340.21</v>
+        <v>156.48</v>
       </c>
       <c r="K260" s="4" t="n">
-        <v>332.25</v>
-      </c>
-      <c r="L260" s="6">
+        <v>160.73</v>
+      </c>
+      <c r="L260" s="5">
         <f>F260*(K260-J260)</f>
         <v/>
       </c>
@@ -9582,29 +9687,29 @@
     <row r="261" ht="16.5" customHeight="1">
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>台表科(6278)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E261" s="3" t="n">
-        <v>584</v>
+        <v>167</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>12458</v>
+        <v>25941</v>
       </c>
       <c r="H261" s="3" t="n">
-        <v>1215</v>
+        <v>17216</v>
       </c>
       <c r="I261" s="3" t="n">
-        <v>11243</v>
+        <v>8725</v>
       </c>
       <c r="J261" s="4" t="n">
-        <v>213.33</v>
+        <v>1553.35</v>
       </c>
       <c r="K261" s="4" t="n">
-        <v>209.47</v>
+        <v>1550.99</v>
       </c>
       <c r="L261" s="6">
         <f>F261*(K261-J261)</f>
@@ -9614,29 +9719,29 @@
     <row r="262" ht="16.5" customHeight="1">
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>瑞昱(2379)</t>
+          <t>健策(3653)</t>
         </is>
       </c>
       <c r="E262" s="3" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F262" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>1543</v>
+        <v>21220</v>
       </c>
       <c r="H262" s="3" t="n">
-        <v>11576</v>
+        <v>7245</v>
       </c>
       <c r="I262" s="3" t="n">
-        <v>-10033</v>
+        <v>13975</v>
       </c>
       <c r="J262" s="4" t="n">
-        <v>0</v>
+        <v>4003.68</v>
       </c>
       <c r="K262" s="4" t="n">
-        <v>0</v>
+        <v>4025.17</v>
       </c>
       <c r="L262" s="5">
         <f>F262*(K262-J262)</f>
@@ -9646,31 +9751,31 @@
     <row r="263" ht="16.5" customHeight="1">
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E263" s="3" t="n">
-        <v>0</v>
+        <v>566</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>0</v>
+        <v>4259</v>
       </c>
       <c r="G263" s="3" t="n">
-        <v>108</v>
+        <v>17015</v>
       </c>
       <c r="H263" s="3" t="n">
-        <v>10836</v>
+        <v>127950</v>
       </c>
       <c r="I263" s="3" t="n">
-        <v>-10728</v>
+        <v>-110935</v>
       </c>
       <c r="J263" s="4" t="n">
-        <v>0</v>
+        <v>300.62</v>
       </c>
       <c r="K263" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L263" s="5">
+        <v>300.42</v>
+      </c>
+      <c r="L263" s="6">
         <f>F263*(K263-J263)</f>
         <v/>
       </c>
@@ -9678,31 +9783,31 @@
     <row r="264" ht="16.5" customHeight="1">
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>大聯大(3702)</t>
+          <t>中砂(1560)</t>
         </is>
       </c>
       <c r="E264" s="3" t="n">
-        <v>446</v>
+        <v>93</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>7</v>
+        <v>745</v>
       </c>
       <c r="G264" s="3" t="n">
-        <v>0</v>
+        <v>5850</v>
       </c>
       <c r="H264" s="3" t="n">
-        <v>0</v>
+        <v>46853</v>
       </c>
       <c r="I264" s="3" t="n">
-        <v>0</v>
+        <v>-41003</v>
       </c>
       <c r="J264" s="4" t="n">
-        <v>0</v>
+        <v>629</v>
       </c>
       <c r="K264" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L264" s="5">
+        <v>628.9</v>
+      </c>
+      <c r="L264" s="6">
         <f>F264*(K264-J264)</f>
         <v/>
       </c>
@@ -9777,31 +9882,31 @@
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E266" s="3" t="n">
-        <v>0</v>
+        <v>7837</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>0</v>
+        <v>1573</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>72645</v>
+        <v>235855</v>
       </c>
       <c r="H266" s="3" t="n">
-        <v>5632</v>
+        <v>47190</v>
       </c>
       <c r="I266" s="3" t="n">
-        <v>67013</v>
+        <v>188665</v>
       </c>
       <c r="J266" s="4" t="n">
-        <v>0</v>
+        <v>300.95</v>
       </c>
       <c r="K266" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L266" s="5">
+        <v>300</v>
+      </c>
+      <c r="L266" s="6">
         <f>F266*(K266-J266)</f>
         <v/>
       </c>
@@ -9809,29 +9914,29 @@
     <row r="267" ht="16.5" customHeight="1">
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E267" s="3" t="n">
-        <v>3667</v>
+        <v>39161</v>
       </c>
       <c r="F267" s="3" t="n">
-        <v>279</v>
+        <v>719</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>59828</v>
+        <v>126131</v>
       </c>
       <c r="H267" s="3" t="n">
-        <v>4330</v>
+        <v>2297</v>
       </c>
       <c r="I267" s="3" t="n">
-        <v>55498</v>
+        <v>123834</v>
       </c>
       <c r="J267" s="4" t="n">
-        <v>163.15</v>
+        <v>32.21</v>
       </c>
       <c r="K267" s="4" t="n">
-        <v>155.19</v>
+        <v>31.94</v>
       </c>
       <c r="L267" s="6">
         <f>F267*(K267-J267)</f>
@@ -9841,31 +9946,31 @@
     <row r="268" ht="16.5" customHeight="1">
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E268" s="3" t="n">
-        <v>2115</v>
+        <v>272</v>
       </c>
       <c r="F268" s="3" t="n">
-        <v>709</v>
+        <v>21</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>55936</v>
+        <v>72645</v>
       </c>
       <c r="H268" s="3" t="n">
-        <v>18665</v>
+        <v>5632</v>
       </c>
       <c r="I268" s="3" t="n">
-        <v>37271</v>
+        <v>67013</v>
       </c>
       <c r="J268" s="4" t="n">
-        <v>264.47</v>
+        <v>2670.76</v>
       </c>
       <c r="K268" s="4" t="n">
-        <v>263.26</v>
-      </c>
-      <c r="L268" s="6">
+        <v>2681.81</v>
+      </c>
+      <c r="L268" s="5">
         <f>F268*(K268-J268)</f>
         <v/>
       </c>
@@ -9873,31 +9978,31 @@
     <row r="269" ht="16.5" customHeight="1">
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>晶豪科(3006)</t>
         </is>
       </c>
       <c r="E269" s="3" t="n">
-        <v>0</v>
+        <v>2883</v>
       </c>
       <c r="F269" s="3" t="n">
-        <v>0</v>
+        <v>153</v>
       </c>
       <c r="G269" s="3" t="n">
-        <v>49285</v>
+        <v>63762</v>
       </c>
       <c r="H269" s="3" t="n">
-        <v>13014</v>
+        <v>3288</v>
       </c>
       <c r="I269" s="3" t="n">
-        <v>36271</v>
+        <v>60474</v>
       </c>
       <c r="J269" s="4" t="n">
-        <v>0</v>
+        <v>221.17</v>
       </c>
       <c r="K269" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L269" s="5">
+        <v>214.9</v>
+      </c>
+      <c r="L269" s="6">
         <f>F269*(K269-J269)</f>
         <v/>
       </c>
@@ -9905,31 +10010,31 @@
     <row r="270" ht="16.5" customHeight="1">
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E270" s="3" t="n">
-        <v>0</v>
+        <v>5209</v>
       </c>
       <c r="F270" s="3" t="n">
-        <v>0</v>
+        <v>2192</v>
       </c>
       <c r="G270" s="3" t="n">
-        <v>42887</v>
+        <v>61080</v>
       </c>
       <c r="H270" s="3" t="n">
-        <v>1470</v>
+        <v>25317</v>
       </c>
       <c r="I270" s="3" t="n">
-        <v>41417</v>
+        <v>35763</v>
       </c>
       <c r="J270" s="4" t="n">
-        <v>0</v>
+        <v>117.26</v>
       </c>
       <c r="K270" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L270" s="5">
+        <v>115.5</v>
+      </c>
+      <c r="L270" s="6">
         <f>F270*(K270-J270)</f>
         <v/>
       </c>
@@ -9937,29 +10042,29 @@
     <row r="271" ht="16.5" customHeight="1">
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>台表科(6278)</t>
+          <t>中美晶(5483)</t>
         </is>
       </c>
       <c r="E271" s="3" t="n">
-        <v>1082</v>
+        <v>3667</v>
       </c>
       <c r="F271" s="3" t="n">
-        <v>2284</v>
+        <v>279</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>23254</v>
+        <v>59828</v>
       </c>
       <c r="H271" s="3" t="n">
-        <v>46088</v>
+        <v>4330</v>
       </c>
       <c r="I271" s="3" t="n">
-        <v>-22834</v>
+        <v>55498</v>
       </c>
       <c r="J271" s="4" t="n">
-        <v>214.92</v>
+        <v>163.15</v>
       </c>
       <c r="K271" s="4" t="n">
-        <v>201.79</v>
+        <v>155.19</v>
       </c>
       <c r="L271" s="6">
         <f>F271*(K271-J271)</f>
@@ -9969,31 +10074,31 @@
     <row r="272" ht="16.5" customHeight="1">
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E272" s="3" t="n">
-        <v>0</v>
+        <v>2115</v>
       </c>
       <c r="F272" s="3" t="n">
-        <v>0</v>
+        <v>709</v>
       </c>
       <c r="G272" s="3" t="n">
-        <v>20648</v>
+        <v>55936</v>
       </c>
       <c r="H272" s="3" t="n">
-        <v>654</v>
+        <v>18665</v>
       </c>
       <c r="I272" s="3" t="n">
-        <v>19994</v>
+        <v>37271</v>
       </c>
       <c r="J272" s="4" t="n">
-        <v>0</v>
+        <v>264.47</v>
       </c>
       <c r="K272" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L272" s="5">
+        <v>263.26</v>
+      </c>
+      <c r="L272" s="6">
         <f>F272*(K272-J272)</f>
         <v/>
       </c>
@@ -10001,29 +10106,29 @@
     <row r="273" ht="16.5" customHeight="1">
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>宜鼎(5289)</t>
         </is>
       </c>
       <c r="E273" s="3" t="n">
-        <v>51</v>
+        <v>280</v>
       </c>
       <c r="F273" s="3" t="n">
-        <v>839</v>
+        <v>74</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>2553</v>
+        <v>49285</v>
       </c>
       <c r="H273" s="3" t="n">
-        <v>41775</v>
+        <v>13014</v>
       </c>
       <c r="I273" s="3" t="n">
-        <v>-39222</v>
+        <v>36271</v>
       </c>
       <c r="J273" s="4" t="n">
-        <v>500.53</v>
+        <v>1760.19</v>
       </c>
       <c r="K273" s="4" t="n">
-        <v>497.91</v>
+        <v>1758.7</v>
       </c>
       <c r="L273" s="6">
         <f>F273*(K273-J273)</f>
@@ -10033,29 +10138,29 @@
     <row r="274" ht="16.5" customHeight="1">
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>順德(2351)</t>
+          <t>譜瑞-KY(4966)</t>
         </is>
       </c>
       <c r="E274" s="3" t="n">
-        <v>117</v>
+        <v>584</v>
       </c>
       <c r="F274" s="3" t="n">
-        <v>2013</v>
+        <v>20</v>
       </c>
       <c r="G274" s="3" t="n">
-        <v>2166</v>
+        <v>42887</v>
       </c>
       <c r="H274" s="3" t="n">
-        <v>37540</v>
+        <v>1470</v>
       </c>
       <c r="I274" s="3" t="n">
-        <v>-35374</v>
+        <v>41417</v>
       </c>
       <c r="J274" s="4" t="n">
-        <v>185.1</v>
+        <v>734.37</v>
       </c>
       <c r="K274" s="4" t="n">
-        <v>186.49</v>
+        <v>735.1</v>
       </c>
       <c r="L274" s="5">
         <f>F274*(K274-J274)</f>
@@ -10065,29 +10170,29 @@
     <row r="275" ht="16.5" customHeight="1">
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>立隆電(2472)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E275" s="3" t="n">
-        <v>51</v>
+        <v>3172</v>
       </c>
       <c r="F275" s="3" t="n">
-        <v>821</v>
+        <v>22</v>
       </c>
       <c r="G275" s="3" t="n">
-        <v>1134</v>
+        <v>34554</v>
       </c>
       <c r="H275" s="3" t="n">
-        <v>17660</v>
+        <v>233</v>
       </c>
       <c r="I275" s="3" t="n">
-        <v>-16526</v>
+        <v>34321</v>
       </c>
       <c r="J275" s="4" t="n">
-        <v>222.35</v>
+        <v>108.93</v>
       </c>
       <c r="K275" s="4" t="n">
-        <v>215.1</v>
+        <v>105.86</v>
       </c>
       <c r="L275" s="6">
         <f>F275*(K275-J275)</f>
@@ -10210,10 +10315,10 @@
         </is>
       </c>
       <c r="E278" s="3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="F278" s="3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G278" s="3" t="n">
         <v>13793</v>
@@ -10225,12 +10330,12 @@
         <v>10705</v>
       </c>
       <c r="J278" s="4" t="n">
-        <v>0</v>
+        <v>2224.61</v>
       </c>
       <c r="K278" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L278" s="5">
+        <v>2205.93</v>
+      </c>
+      <c r="L278" s="6">
         <f>F278*(K278-J278)</f>
         <v/>
       </c>
@@ -10639,10 +10744,10 @@
         </is>
       </c>
       <c r="E290" s="3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G290" s="3" t="n">
         <v>14676</v>
@@ -10654,12 +10759,12 @@
         <v>-9895</v>
       </c>
       <c r="J290" s="4" t="n">
-        <v>0</v>
+        <v>6380.83</v>
       </c>
       <c r="K290" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L290" s="5">
+        <v>6300.21</v>
+      </c>
+      <c r="L290" s="6">
         <f>F290*(K290-J290)</f>
         <v/>
       </c>
@@ -10994,10 +11099,10 @@
         </is>
       </c>
       <c r="E300" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F300" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G300" s="3" t="n">
         <v>3376</v>
@@ -11009,10 +11114,10 @@
         <v>-5434</v>
       </c>
       <c r="J300" s="4" t="n">
-        <v>0</v>
+        <v>5626</v>
       </c>
       <c r="K300" s="4" t="n">
-        <v>0</v>
+        <v>5873.47</v>
       </c>
       <c r="L300" s="5">
         <f>F300*(K300-J300)</f>
@@ -11058,10 +11163,10 @@
         </is>
       </c>
       <c r="E302" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F302" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G302" s="3" t="n">
         <v>3003</v>
@@ -11073,12 +11178,12 @@
         <v>-4604</v>
       </c>
       <c r="J302" s="4" t="n">
-        <v>0</v>
+        <v>2309.77</v>
       </c>
       <c r="K302" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L302" s="5">
+        <v>2237.26</v>
+      </c>
+      <c r="L302" s="6">
         <f>F302*(K302-J302)</f>
         <v/>
       </c>
@@ -11090,10 +11195,10 @@
         </is>
       </c>
       <c r="E303" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F303" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G303" s="3" t="n">
         <v>1935</v>
@@ -11105,10 +11210,10 @@
         <v>374</v>
       </c>
       <c r="J303" s="4" t="n">
-        <v>0</v>
+        <v>3870.2</v>
       </c>
       <c r="K303" s="4" t="n">
-        <v>0</v>
+        <v>3903.5</v>
       </c>
       <c r="L303" s="5">
         <f>F303*(K303-J303)</f>
@@ -11122,10 +11227,10 @@
         </is>
       </c>
       <c r="E304" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F304" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G304" s="3" t="n">
         <v>1875</v>
@@ -11137,10 +11242,10 @@
         <v>1675</v>
       </c>
       <c r="J304" s="4" t="n">
-        <v>0</v>
+        <v>852.23</v>
       </c>
       <c r="K304" s="4" t="n">
-        <v>0</v>
+        <v>1001.5</v>
       </c>
       <c r="L304" s="5">
         <f>F304*(K304-J304)</f>
@@ -11154,10 +11259,10 @@
         </is>
       </c>
       <c r="E305" s="3" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="F305" s="3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G305" s="3" t="n">
         <v>1798</v>
@@ -11169,12 +11274,12 @@
         <v>490</v>
       </c>
       <c r="J305" s="4" t="n">
-        <v>0</v>
+        <v>243.01</v>
       </c>
       <c r="K305" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L305" s="5">
+        <v>242.3</v>
+      </c>
+      <c r="L305" s="6">
         <f>F305*(K305-J305)</f>
         <v/>
       </c>
@@ -11186,7 +11291,7 @@
         </is>
       </c>
       <c r="E306" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F306" s="3" t="n">
         <v>0</v>
@@ -11201,7 +11306,7 @@
         <v>1620</v>
       </c>
       <c r="J306" s="4" t="n">
-        <v>0</v>
+        <v>5443.67</v>
       </c>
       <c r="K306" s="4" t="n">
         <v>0</v>
@@ -11250,10 +11355,10 @@
         </is>
       </c>
       <c r="E308" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F308" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G308" s="3" t="n">
         <v>1231</v>
@@ -11265,10 +11370,10 @@
         <v>452</v>
       </c>
       <c r="J308" s="4" t="n">
-        <v>0</v>
+        <v>1538.75</v>
       </c>
       <c r="K308" s="4" t="n">
-        <v>0</v>
+        <v>1557.6</v>
       </c>
       <c r="L308" s="5">
         <f>F308*(K308-J308)</f>
@@ -11349,10 +11454,10 @@
         </is>
       </c>
       <c r="E310" s="3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F310" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G310" s="3" t="n">
         <v>9463</v>
@@ -11364,12 +11469,12 @@
         <v>8842</v>
       </c>
       <c r="J310" s="4" t="n">
-        <v>0</v>
+        <v>2253.17</v>
       </c>
       <c r="K310" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L310" s="5">
+        <v>2070.67</v>
+      </c>
+      <c r="L310" s="6">
         <f>F310*(K310-J310)</f>
         <v/>
       </c>
@@ -11445,10 +11550,10 @@
         </is>
       </c>
       <c r="E313" s="3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F313" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G313" s="3" t="n">
         <v>3839</v>
@@ -11460,12 +11565,12 @@
         <v>2232</v>
       </c>
       <c r="J313" s="4" t="n">
-        <v>0</v>
+        <v>673.49</v>
       </c>
       <c r="K313" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L313" s="5">
+        <v>669.62</v>
+      </c>
+      <c r="L313" s="6">
         <f>F313*(K313-J313)</f>
         <v/>
       </c>
@@ -11509,10 +11614,10 @@
         </is>
       </c>
       <c r="E315" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F315" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G315" s="3" t="n">
         <v>2814</v>
@@ -11524,10 +11629,10 @@
         <v>2282</v>
       </c>
       <c r="J315" s="4" t="n">
-        <v>0</v>
+        <v>4019.43</v>
       </c>
       <c r="K315" s="4" t="n">
-        <v>0</v>
+        <v>5315</v>
       </c>
       <c r="L315" s="5">
         <f>F315*(K315-J315)</f>
@@ -11605,10 +11710,10 @@
         </is>
       </c>
       <c r="E318" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F318" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G318" s="3" t="n">
         <v>2166</v>
@@ -11620,10 +11725,10 @@
         <v>509</v>
       </c>
       <c r="J318" s="4" t="n">
-        <v>0</v>
+        <v>902.46</v>
       </c>
       <c r="K318" s="4" t="n">
-        <v>0</v>
+        <v>920.61</v>
       </c>
       <c r="L318" s="5">
         <f>F318*(K318-J318)</f>
@@ -11736,10 +11841,10 @@
         </is>
       </c>
       <c r="E321" s="3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F321" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G321" s="3" t="n">
         <v>16529</v>
@@ -11751,10 +11856,10 @@
         <v>13416</v>
       </c>
       <c r="J321" s="4" t="n">
-        <v>0</v>
+        <v>3843.91</v>
       </c>
       <c r="K321" s="4" t="n">
-        <v>0</v>
+        <v>3890.75</v>
       </c>
       <c r="L321" s="5">
         <f>F321*(K321-J321)</f>
@@ -11768,10 +11873,10 @@
         </is>
       </c>
       <c r="E322" s="3" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G322" s="3" t="n">
         <v>15862</v>
@@ -11783,10 +11888,10 @@
         <v>1772</v>
       </c>
       <c r="J322" s="4" t="n">
-        <v>0</v>
+        <v>2234.03</v>
       </c>
       <c r="K322" s="4" t="n">
-        <v>0</v>
+        <v>2236.56</v>
       </c>
       <c r="L322" s="5">
         <f>F322*(K322-J322)</f>
@@ -11896,10 +12001,10 @@
         </is>
       </c>
       <c r="E326" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F326" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G326" s="3" t="n">
         <v>6063</v>
@@ -11911,12 +12016,12 @@
         <v>1000</v>
       </c>
       <c r="J326" s="4" t="n">
-        <v>0</v>
+        <v>1837.3</v>
       </c>
       <c r="K326" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L326" s="5">
+        <v>1808.25</v>
+      </c>
+      <c r="L326" s="6">
         <f>F326*(K326-J326)</f>
         <v/>
       </c>
@@ -11928,10 +12033,10 @@
         </is>
       </c>
       <c r="E327" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F327" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G327" s="3" t="n">
         <v>5885</v>
@@ -11943,10 +12048,10 @@
         <v>2570</v>
       </c>
       <c r="J327" s="4" t="n">
-        <v>0</v>
+        <v>5349.91</v>
       </c>
       <c r="K327" s="4" t="n">
-        <v>0</v>
+        <v>5524.67</v>
       </c>
       <c r="L327" s="5">
         <f>F327*(K327-J327)</f>
@@ -12155,10 +12260,10 @@
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F333" s="3" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="G333" s="3" t="n">
         <v>4938</v>
@@ -12170,12 +12275,12 @@
         <v>1207</v>
       </c>
       <c r="J333" s="4" t="n">
-        <v>0</v>
+        <v>461.49</v>
       </c>
       <c r="K333" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L333" s="5">
+        <v>460.57</v>
+      </c>
+      <c r="L333" s="6">
         <f>F333*(K333-J333)</f>
         <v/>
       </c>
@@ -12315,10 +12420,10 @@
         </is>
       </c>
       <c r="E338" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F338" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G338" s="3" t="n">
         <v>2516</v>
@@ -12330,12 +12435,12 @@
         <v>1532</v>
       </c>
       <c r="J338" s="4" t="n">
-        <v>0</v>
+        <v>5031.8</v>
       </c>
       <c r="K338" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L338" s="5">
+        <v>4917.5</v>
+      </c>
+      <c r="L338" s="6">
         <f>F338*(K338-J338)</f>
         <v/>
       </c>
@@ -12407,29 +12512,29 @@
     <row r="341" ht="16.5" customHeight="1">
       <c r="D341" s="2" t="inlineStr">
         <is>
-          <t>華通(2313)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E341" s="3" t="n">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>41</v>
+        <v>570</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="H341" s="3" t="n">
-        <v>1030</v>
+        <v>1841</v>
       </c>
       <c r="I341" s="3" t="n">
-        <v>1000</v>
+        <v>204</v>
       </c>
       <c r="J341" s="4" t="n">
-        <v>247.59</v>
+        <v>32.3</v>
       </c>
       <c r="K341" s="4" t="n">
-        <v>251.27</v>
+        <v>32.3</v>
       </c>
       <c r="L341" s="5">
         <f>F341*(K341-J341)</f>
@@ -12734,10 +12839,10 @@
         </is>
       </c>
       <c r="E350" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G350" s="3" t="n">
         <v>1698</v>
@@ -12749,12 +12854,12 @@
         <v>-494</v>
       </c>
       <c r="J350" s="4" t="n">
-        <v>0</v>
+        <v>5661.33</v>
       </c>
       <c r="K350" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L350" s="5">
+        <v>5478.75</v>
+      </c>
+      <c r="L350" s="6">
         <f>F350*(K350-J350)</f>
         <v/>
       </c>
@@ -12766,10 +12871,10 @@
         </is>
       </c>
       <c r="E351" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G351" s="3" t="n">
         <v>1544</v>
@@ -12781,12 +12886,12 @@
         <v>374</v>
       </c>
       <c r="J351" s="4" t="n">
-        <v>0</v>
+        <v>395.85</v>
       </c>
       <c r="K351" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L351" s="5">
+        <v>389.83</v>
+      </c>
+      <c r="L351" s="6">
         <f>F351*(K351-J351)</f>
         <v/>
       </c>
@@ -12929,10 +13034,10 @@
         </is>
       </c>
       <c r="E355" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G355" s="3" t="n">
         <v>5758</v>
@@ -12944,10 +13049,10 @@
         <v>4813</v>
       </c>
       <c r="J355" s="4" t="n">
-        <v>0</v>
+        <v>2214.81</v>
       </c>
       <c r="K355" s="4" t="n">
-        <v>0</v>
+        <v>2363.5</v>
       </c>
       <c r="L355" s="5">
         <f>F355*(K355-J355)</f>
@@ -13025,10 +13130,10 @@
         </is>
       </c>
       <c r="E358" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F358" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G358" s="3" t="n">
         <v>1749</v>
@@ -13040,10 +13145,10 @@
         <v>1643</v>
       </c>
       <c r="J358" s="4" t="n">
-        <v>0</v>
+        <v>920.63</v>
       </c>
       <c r="K358" s="4" t="n">
-        <v>0</v>
+        <v>1056</v>
       </c>
       <c r="L358" s="5">
         <f>F358*(K358-J358)</f>
@@ -13089,10 +13194,10 @@
         </is>
       </c>
       <c r="E360" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G360" s="3" t="n">
         <v>1387</v>
@@ -13104,10 +13209,10 @@
         <v>304</v>
       </c>
       <c r="J360" s="4" t="n">
-        <v>0</v>
+        <v>4622.67</v>
       </c>
       <c r="K360" s="4" t="n">
-        <v>0</v>
+        <v>5415.5</v>
       </c>
       <c r="L360" s="5">
         <f>F360*(K360-J360)</f>
@@ -13185,10 +13290,10 @@
         </is>
       </c>
       <c r="E363" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G363" s="3" t="n">
         <v>1227</v>
@@ -13200,12 +13305,12 @@
         <v>-1555</v>
       </c>
       <c r="J363" s="4" t="n">
-        <v>0</v>
+        <v>4091.33</v>
       </c>
       <c r="K363" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L363" s="5">
+        <v>3974.14</v>
+      </c>
+      <c r="L363" s="6">
         <f>F363*(K363-J363)</f>
         <v/>
       </c>
@@ -13354,29 +13459,29 @@
     <row r="367" ht="16.5" customHeight="1">
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E367" s="3" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="F367" s="3" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
       <c r="G367" s="3" t="n">
-        <v>3489</v>
+        <v>5223</v>
       </c>
       <c r="H367" s="3" t="n">
-        <v>4715</v>
+        <v>5877</v>
       </c>
       <c r="I367" s="3" t="n">
-        <v>-1226</v>
+        <v>-654</v>
       </c>
       <c r="J367" s="4" t="n">
-        <v>0</v>
+        <v>300.16</v>
       </c>
       <c r="K367" s="4" t="n">
-        <v>0</v>
+        <v>301.36</v>
       </c>
       <c r="L367" s="5">
         <f>F367*(K367-J367)</f>
@@ -13386,31 +13491,31 @@
     <row r="368" ht="16.5" customHeight="1">
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>家登(3680)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E368" s="3" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G368" s="3" t="n">
-        <v>1154</v>
+        <v>3874</v>
       </c>
       <c r="H368" s="3" t="n">
-        <v>559</v>
+        <v>826</v>
       </c>
       <c r="I368" s="3" t="n">
-        <v>595</v>
+        <v>3048</v>
       </c>
       <c r="J368" s="4" t="n">
-        <v>0</v>
+        <v>490.38</v>
       </c>
       <c r="K368" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L368" s="5">
+        <v>486.06</v>
+      </c>
+      <c r="L368" s="6">
         <f>F368*(K368-J368)</f>
         <v/>
       </c>
@@ -13418,29 +13523,29 @@
     <row r="369" ht="16.5" customHeight="1">
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>普萊德(6263)</t>
+          <t>宜鼎(5289)</t>
         </is>
       </c>
       <c r="E369" s="3" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F369" s="3" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G369" s="3" t="n">
-        <v>1008</v>
+        <v>3489</v>
       </c>
       <c r="H369" s="3" t="n">
-        <v>50</v>
+        <v>4715</v>
       </c>
       <c r="I369" s="3" t="n">
-        <v>958</v>
+        <v>-1226</v>
       </c>
       <c r="J369" s="4" t="n">
-        <v>168</v>
+        <v>1744.65</v>
       </c>
       <c r="K369" s="4" t="n">
-        <v>168</v>
+        <v>1746.41</v>
       </c>
       <c r="L369" s="5">
         <f>F369*(K369-J369)</f>
@@ -13450,29 +13555,29 @@
     <row r="370" ht="16.5" customHeight="1">
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>鴻勁(7769)</t>
         </is>
       </c>
       <c r="E370" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G370" s="3" t="n">
-        <v>939</v>
+        <v>2954</v>
       </c>
       <c r="H370" s="3" t="n">
-        <v>60</v>
+        <v>3480</v>
       </c>
       <c r="I370" s="3" t="n">
-        <v>879</v>
+        <v>-526</v>
       </c>
       <c r="J370" s="4" t="n">
-        <v>0</v>
+        <v>5907.4</v>
       </c>
       <c r="K370" s="4" t="n">
-        <v>0</v>
+        <v>6959.6</v>
       </c>
       <c r="L370" s="5">
         <f>F370*(K370-J370)</f>
@@ -13482,29 +13587,29 @@
     <row r="371" ht="16.5" customHeight="1">
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>信昌電(6173)</t>
+          <t>華新科(2492)</t>
         </is>
       </c>
       <c r="E371" s="3" t="n">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="F371" s="3" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G371" s="3" t="n">
-        <v>248</v>
+        <v>1529</v>
       </c>
       <c r="H371" s="3" t="n">
-        <v>847</v>
+        <v>1103</v>
       </c>
       <c r="I371" s="3" t="n">
-        <v>-599</v>
+        <v>426</v>
       </c>
       <c r="J371" s="4" t="n">
-        <v>124.05</v>
+        <v>171.82</v>
       </c>
       <c r="K371" s="4" t="n">
-        <v>126.39</v>
+        <v>172.3</v>
       </c>
       <c r="L371" s="5">
         <f>F371*(K371-J371)</f>
@@ -13514,31 +13619,31 @@
     <row r="372" ht="16.5" customHeight="1">
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E372" s="3" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="G372" s="3" t="n">
-        <v>48</v>
+        <v>1251</v>
       </c>
       <c r="H372" s="3" t="n">
-        <v>4586</v>
+        <v>2012</v>
       </c>
       <c r="I372" s="3" t="n">
-        <v>-4538</v>
+        <v>-761</v>
       </c>
       <c r="J372" s="4" t="n">
-        <v>239.5</v>
+        <v>347.58</v>
       </c>
       <c r="K372" s="4" t="n">
-        <v>260.56</v>
-      </c>
-      <c r="L372" s="5">
+        <v>340.93</v>
+      </c>
+      <c r="L372" s="6">
         <f>F372*(K372-J372)</f>
         <v/>
       </c>
@@ -13546,29 +13651,29 @@
     <row r="373" ht="16.5" customHeight="1">
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>現觀科(6906)</t>
+          <t>康舒(6282)</t>
         </is>
       </c>
       <c r="E373" s="3" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="F373" s="3" t="n">
-        <v>74</v>
+        <v>261</v>
       </c>
       <c r="G373" s="3" t="n">
-        <v>0</v>
+        <v>1213</v>
       </c>
       <c r="H373" s="3" t="n">
-        <v>512</v>
+        <v>1446</v>
       </c>
       <c r="I373" s="3" t="n">
-        <v>-512</v>
+        <v>-233</v>
       </c>
       <c r="J373" s="4" t="n">
-        <v>0</v>
+        <v>55.4</v>
       </c>
       <c r="K373" s="4" t="n">
-        <v>69.23</v>
+        <v>55.4</v>
       </c>
       <c r="L373" s="5">
         <f>F373*(K373-J373)</f>
@@ -13576,15 +13681,36 @@
       </c>
     </row>
     <row r="374" ht="16.5" customHeight="1">
-      <c r="D374" s="2" t="n"/>
-      <c r="E374" s="3" t="n"/>
-      <c r="F374" s="3" t="n"/>
-      <c r="G374" s="3" t="n"/>
-      <c r="H374" s="3" t="n"/>
-      <c r="I374" s="3" t="n"/>
-      <c r="J374" s="4" t="n"/>
-      <c r="K374" s="4" t="n"/>
-      <c r="L374" s="5" t="n"/>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>家登(3680)</t>
+        </is>
+      </c>
+      <c r="E374" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F374" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G374" s="3" t="n">
+        <v>1154</v>
+      </c>
+      <c r="H374" s="3" t="n">
+        <v>559</v>
+      </c>
+      <c r="I374" s="3" t="n">
+        <v>595</v>
+      </c>
+      <c r="J374" s="4" t="n">
+        <v>607.42</v>
+      </c>
+      <c r="K374" s="4" t="n">
+        <v>621</v>
+      </c>
+      <c r="L374" s="5">
+        <f>F374*(K374-J374)</f>
+        <v/>
+      </c>
     </row>
     <row r="375" ht="16.5" customHeight="1">
       <c r="A375" s="1" t="inlineStr">
@@ -13666,29 +13792,29 @@
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E376" s="3" t="n">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="F376" s="3" t="n">
-        <v>0</v>
+        <v>640</v>
       </c>
       <c r="G376" s="3" t="n">
-        <v>5416</v>
+        <v>23143</v>
       </c>
       <c r="H376" s="3" t="n">
-        <v>2224</v>
+        <v>19256</v>
       </c>
       <c r="I376" s="3" t="n">
-        <v>3192</v>
+        <v>3887</v>
       </c>
       <c r="J376" s="4" t="n">
-        <v>0</v>
+        <v>298.62</v>
       </c>
       <c r="K376" s="4" t="n">
-        <v>0</v>
+        <v>300.88</v>
       </c>
       <c r="L376" s="5">
         <f>F376*(K376-J376)</f>
@@ -13698,29 +13824,29 @@
     <row r="377" ht="16.5" customHeight="1">
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E377" s="3" t="n">
-        <v>201</v>
+        <v>6122</v>
       </c>
       <c r="F377" s="3" t="n">
-        <v>110</v>
+        <v>617</v>
       </c>
       <c r="G377" s="3" t="n">
-        <v>5316</v>
+        <v>19702</v>
       </c>
       <c r="H377" s="3" t="n">
-        <v>2906</v>
+        <v>1973</v>
       </c>
       <c r="I377" s="3" t="n">
-        <v>2410</v>
+        <v>17729</v>
       </c>
       <c r="J377" s="4" t="n">
-        <v>264.5</v>
+        <v>32.18</v>
       </c>
       <c r="K377" s="4" t="n">
-        <v>264.22</v>
+        <v>31.98</v>
       </c>
       <c r="L377" s="6">
         <f>F377*(K377-J377)</f>
@@ -13730,29 +13856,29 @@
     <row r="378" ht="16.5" customHeight="1">
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>順德(2351)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E378" s="3" t="n">
-        <v>150</v>
+        <v>748</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>58</v>
+        <v>686</v>
       </c>
       <c r="G378" s="3" t="n">
-        <v>2775</v>
+        <v>8646</v>
       </c>
       <c r="H378" s="3" t="n">
-        <v>1106</v>
+        <v>7930</v>
       </c>
       <c r="I378" s="3" t="n">
-        <v>1669</v>
+        <v>716</v>
       </c>
       <c r="J378" s="4" t="n">
-        <v>185</v>
+        <v>115.59</v>
       </c>
       <c r="K378" s="4" t="n">
-        <v>190.71</v>
+        <v>115.6</v>
       </c>
       <c r="L378" s="5">
         <f>F378*(K378-J378)</f>
@@ -13762,29 +13888,29 @@
     <row r="379" ht="16.5" customHeight="1">
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>昇達科(3491)</t>
         </is>
       </c>
       <c r="E379" s="3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G379" s="3" t="n">
-        <v>1629</v>
+        <v>5416</v>
       </c>
       <c r="H379" s="3" t="n">
-        <v>277</v>
+        <v>2224</v>
       </c>
       <c r="I379" s="3" t="n">
-        <v>1352</v>
+        <v>3192</v>
       </c>
       <c r="J379" s="4" t="n">
-        <v>0</v>
+        <v>1805.47</v>
       </c>
       <c r="K379" s="4" t="n">
-        <v>0</v>
+        <v>1853.58</v>
       </c>
       <c r="L379" s="5">
         <f>F379*(K379-J379)</f>
@@ -13794,31 +13920,31 @@
     <row r="380" ht="16.5" customHeight="1">
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>統新(6426)</t>
+          <t>文曄(3036)</t>
         </is>
       </c>
       <c r="E380" s="3" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="G380" s="3" t="n">
-        <v>803</v>
+        <v>5316</v>
       </c>
       <c r="H380" s="3" t="n">
-        <v>78</v>
+        <v>2906</v>
       </c>
       <c r="I380" s="3" t="n">
-        <v>725</v>
+        <v>2410</v>
       </c>
       <c r="J380" s="4" t="n">
-        <v>0</v>
+        <v>264.5</v>
       </c>
       <c r="K380" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L380" s="5">
+        <v>264.22</v>
+      </c>
+      <c r="L380" s="6">
         <f>F380*(K380-J380)</f>
         <v/>
       </c>
@@ -13826,31 +13952,31 @@
     <row r="381" ht="16.5" customHeight="1">
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E381" s="3" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G381" s="3" t="n">
-        <v>774</v>
+        <v>2650</v>
       </c>
       <c r="H381" s="3" t="n">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="I381" s="3" t="n">
-        <v>596</v>
+        <v>2405</v>
       </c>
       <c r="J381" s="4" t="n">
-        <v>0</v>
+        <v>490.67</v>
       </c>
       <c r="K381" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L381" s="5">
+        <v>490.6</v>
+      </c>
+      <c r="L381" s="6">
         <f>F381*(K381-J381)</f>
         <v/>
       </c>
@@ -13858,29 +13984,29 @@
     <row r="382" ht="16.5" customHeight="1">
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E382" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G382" s="3" t="n">
-        <v>238</v>
+        <v>1629</v>
       </c>
       <c r="H382" s="3" t="n">
-        <v>590</v>
+        <v>277</v>
       </c>
       <c r="I382" s="3" t="n">
-        <v>-352</v>
+        <v>1352</v>
       </c>
       <c r="J382" s="4" t="n">
-        <v>0</v>
+        <v>2714.5</v>
       </c>
       <c r="K382" s="4" t="n">
-        <v>0</v>
+        <v>2771</v>
       </c>
       <c r="L382" s="5">
         <f>F382*(K382-J382)</f>
@@ -13890,29 +14016,29 @@
     <row r="383" ht="16.5" customHeight="1">
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>德微(3675)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E383" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G383" s="3" t="n">
-        <v>121</v>
+        <v>774</v>
       </c>
       <c r="H383" s="3" t="n">
-        <v>553</v>
+        <v>178</v>
       </c>
       <c r="I383" s="3" t="n">
-        <v>-432</v>
+        <v>596</v>
       </c>
       <c r="J383" s="4" t="n">
-        <v>0</v>
+        <v>1548</v>
       </c>
       <c r="K383" s="4" t="n">
-        <v>0</v>
+        <v>1785</v>
       </c>
       <c r="L383" s="5">
         <f>F383*(K383-J383)</f>
@@ -13932,19 +14058,19 @@
         <v>16</v>
       </c>
       <c r="G384" s="3" t="n">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="H384" s="3" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I384" s="3" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="J384" s="4" t="n">
-        <v>0</v>
+        <v>80.3</v>
       </c>
       <c r="K384" s="4" t="n">
-        <v>0</v>
+        <v>80.31</v>
       </c>
       <c r="L384" s="5">
         <f>F384*(K384-J384)</f>
@@ -13954,31 +14080,31 @@
     <row r="385" ht="16.5" customHeight="1">
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>閎康(3587)</t>
+          <t>昶昕(8438)</t>
         </is>
       </c>
       <c r="E385" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F385" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G385" s="3" t="n">
-        <v>0</v>
+        <v>365</v>
       </c>
       <c r="H385" s="3" t="n">
-        <v>420</v>
+        <v>20</v>
       </c>
       <c r="I385" s="3" t="n">
-        <v>-420</v>
+        <v>345</v>
       </c>
       <c r="J385" s="4" t="n">
-        <v>0</v>
+        <v>98.7</v>
       </c>
       <c r="K385" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L385" s="5">
+        <v>98.5</v>
+      </c>
+      <c r="L385" s="6">
         <f>F385*(K385-J385)</f>
         <v/>
       </c>
@@ -14053,31 +14179,31 @@
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>昇達科(3491)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E387" s="3" t="n">
-        <v>0</v>
+        <v>287</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="G387" s="3" t="n">
-        <v>6063</v>
+        <v>8642</v>
       </c>
       <c r="H387" s="3" t="n">
-        <v>5063</v>
+        <v>4991</v>
       </c>
       <c r="I387" s="3" t="n">
-        <v>1000</v>
+        <v>3651</v>
       </c>
       <c r="J387" s="4" t="n">
-        <v>0</v>
+        <v>301.1</v>
       </c>
       <c r="K387" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L387" s="5">
+        <v>300.68</v>
+      </c>
+      <c r="L387" s="6">
         <f>F387*(K387-J387)</f>
         <v/>
       </c>
@@ -14085,29 +14211,29 @@
     <row r="388" ht="16.5" customHeight="1">
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>台半(5425)</t>
+          <t>昇達科(3491)</t>
         </is>
       </c>
       <c r="E388" s="3" t="n">
-        <v>486</v>
+        <v>33</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>317</v>
+        <v>28</v>
       </c>
       <c r="G388" s="3" t="n">
-        <v>3851</v>
+        <v>6063</v>
       </c>
       <c r="H388" s="3" t="n">
-        <v>2483</v>
+        <v>5063</v>
       </c>
       <c r="I388" s="3" t="n">
-        <v>1368</v>
+        <v>1000</v>
       </c>
       <c r="J388" s="4" t="n">
-        <v>79.25</v>
+        <v>1837.3</v>
       </c>
       <c r="K388" s="4" t="n">
-        <v>78.33</v>
+        <v>1808.25</v>
       </c>
       <c r="L388" s="6">
         <f>F388*(K388-J388)</f>
@@ -14117,31 +14243,31 @@
     <row r="389" ht="16.5" customHeight="1">
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E389" s="3" t="n">
-        <v>0</v>
+        <v>1322</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="G389" s="3" t="n">
-        <v>2254</v>
+        <v>4258</v>
       </c>
       <c r="H389" s="3" t="n">
-        <v>1275</v>
+        <v>2185</v>
       </c>
       <c r="I389" s="3" t="n">
-        <v>979</v>
+        <v>2073</v>
       </c>
       <c r="J389" s="4" t="n">
-        <v>0</v>
+        <v>32.21</v>
       </c>
       <c r="K389" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L389" s="5">
+        <v>31.94</v>
+      </c>
+      <c r="L389" s="6">
         <f>F389*(K389-J389)</f>
         <v/>
       </c>
@@ -14149,31 +14275,31 @@
     <row r="390" ht="16.5" customHeight="1">
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>德微(3675)</t>
+          <t>台半(5425)</t>
         </is>
       </c>
       <c r="E390" s="3" t="n">
-        <v>45</v>
+        <v>486</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
       <c r="G390" s="3" t="n">
-        <v>1118</v>
+        <v>3851</v>
       </c>
       <c r="H390" s="3" t="n">
-        <v>25</v>
+        <v>2483</v>
       </c>
       <c r="I390" s="3" t="n">
-        <v>1093</v>
+        <v>1368</v>
       </c>
       <c r="J390" s="4" t="n">
-        <v>248.33</v>
+        <v>79.25</v>
       </c>
       <c r="K390" s="4" t="n">
-        <v>249</v>
-      </c>
-      <c r="L390" s="5">
+        <v>78.33</v>
+      </c>
+      <c r="L390" s="6">
         <f>F390*(K390-J390)</f>
         <v/>
       </c>
@@ -14181,29 +14307,29 @@
     <row r="391" ht="16.5" customHeight="1">
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>台表科(6278)</t>
+          <t>矽力*-KY(6415)</t>
         </is>
       </c>
       <c r="E391" s="3" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="F391" s="3" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="G391" s="3" t="n">
-        <v>582</v>
+        <v>3157</v>
       </c>
       <c r="H391" s="3" t="n">
-        <v>1577</v>
+        <v>1847</v>
       </c>
       <c r="I391" s="3" t="n">
-        <v>-995</v>
+        <v>1310</v>
       </c>
       <c r="J391" s="4" t="n">
-        <v>0</v>
+        <v>471.13</v>
       </c>
       <c r="K391" s="4" t="n">
-        <v>0</v>
+        <v>473.67</v>
       </c>
       <c r="L391" s="5">
         <f>F391*(K391-J391)</f>
@@ -14213,31 +14339,31 @@
     <row r="392" ht="16.5" customHeight="1">
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>盟立(2464)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E392" s="3" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>113</v>
+        <v>1272</v>
       </c>
       <c r="G392" s="3" t="n">
-        <v>349</v>
+        <v>1661</v>
       </c>
       <c r="H392" s="3" t="n">
-        <v>1340</v>
+        <v>14895</v>
       </c>
       <c r="I392" s="3" t="n">
-        <v>-991</v>
+        <v>-13234</v>
       </c>
       <c r="J392" s="4" t="n">
-        <v>120.34</v>
+        <v>114.57</v>
       </c>
       <c r="K392" s="4" t="n">
-        <v>118.58</v>
-      </c>
-      <c r="L392" s="6">
+        <v>117.1</v>
+      </c>
+      <c r="L392" s="5">
         <f>F392*(K392-J392)</f>
         <v/>
       </c>
@@ -14245,31 +14371,31 @@
     <row r="393" ht="16.5" customHeight="1">
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>信昌電(6173)</t>
+          <t>德微(3675)</t>
         </is>
       </c>
       <c r="E393" s="3" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F393" s="3" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="G393" s="3" t="n">
-        <v>336</v>
+        <v>1118</v>
       </c>
       <c r="H393" s="3" t="n">
-        <v>1298</v>
+        <v>25</v>
       </c>
       <c r="I393" s="3" t="n">
-        <v>-962</v>
+        <v>1093</v>
       </c>
       <c r="J393" s="4" t="n">
-        <v>129.23</v>
+        <v>248.33</v>
       </c>
       <c r="K393" s="4" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="L393" s="6">
+        <v>249</v>
+      </c>
+      <c r="L393" s="5">
         <f>F393*(K393-J393)</f>
         <v/>
       </c>
@@ -14277,31 +14403,31 @@
     <row r="394" ht="16.5" customHeight="1">
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E394" s="3" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G394" s="3" t="n">
-        <v>324</v>
+        <v>1074</v>
       </c>
       <c r="H394" s="3" t="n">
-        <v>870</v>
+        <v>305</v>
       </c>
       <c r="I394" s="3" t="n">
-        <v>-546</v>
+        <v>769</v>
       </c>
       <c r="J394" s="4" t="n">
-        <v>0</v>
+        <v>108.46</v>
       </c>
       <c r="K394" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L394" s="5">
+        <v>105.14</v>
+      </c>
+      <c r="L394" s="6">
         <f>F394*(K394-J394)</f>
         <v/>
       </c>
@@ -14309,31 +14435,31 @@
     <row r="395" ht="16.5" customHeight="1">
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>榮剛(5009)</t>
+          <t>信昌電(6173)</t>
         </is>
       </c>
       <c r="E395" s="3" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>393</v>
+        <v>105</v>
       </c>
       <c r="G395" s="3" t="n">
-        <v>56</v>
+        <v>336</v>
       </c>
       <c r="H395" s="3" t="n">
-        <v>1575</v>
+        <v>1298</v>
       </c>
       <c r="I395" s="3" t="n">
-        <v>-1519</v>
+        <v>-962</v>
       </c>
       <c r="J395" s="4" t="n">
-        <v>39.71</v>
+        <v>129.23</v>
       </c>
       <c r="K395" s="4" t="n">
-        <v>40.09</v>
-      </c>
-      <c r="L395" s="5">
+        <v>123.6</v>
+      </c>
+      <c r="L395" s="6">
         <f>F395*(K395-J395)</f>
         <v/>
       </c>
@@ -14341,31 +14467,31 @@
     <row r="396" ht="16.5" customHeight="1">
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>文曄(3036)</t>
+          <t>譜瑞-KY(4966)</t>
         </is>
       </c>
       <c r="E396" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F396" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G396" s="3" t="n">
-        <v>52</v>
+        <v>324</v>
       </c>
       <c r="H396" s="3" t="n">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="I396" s="3" t="n">
-        <v>-814</v>
+        <v>-546</v>
       </c>
       <c r="J396" s="4" t="n">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="K396" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L396" s="5">
+        <v>725.33</v>
+      </c>
+      <c r="L396" s="6">
         <f>F396*(K396-J396)</f>
         <v/>
       </c>
@@ -14440,31 +14566,31 @@
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>盟立(2464)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E398" s="3" t="n">
-        <v>266</v>
+        <v>31</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="G398" s="3" t="n">
-        <v>3136</v>
+        <v>935</v>
       </c>
       <c r="H398" s="3" t="n">
-        <v>567</v>
+        <v>3820</v>
       </c>
       <c r="I398" s="3" t="n">
-        <v>2569</v>
+        <v>-2885</v>
       </c>
       <c r="J398" s="4" t="n">
-        <v>117.88</v>
+        <v>301.55</v>
       </c>
       <c r="K398" s="4" t="n">
-        <v>120.62</v>
-      </c>
-      <c r="L398" s="5">
+        <v>300.82</v>
+      </c>
+      <c r="L398" s="6">
         <f>F398*(K398-J398)</f>
         <v/>
       </c>
@@ -14472,29 +14598,29 @@
     <row r="399" ht="16.5" customHeight="1">
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>禾伸堂(3026)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E399" s="3" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>0</v>
+        <v>717</v>
       </c>
       <c r="G399" s="3" t="n">
-        <v>572</v>
+        <v>817</v>
       </c>
       <c r="H399" s="3" t="n">
-        <v>171</v>
+        <v>2304</v>
       </c>
       <c r="I399" s="3" t="n">
-        <v>401</v>
+        <v>-1487</v>
       </c>
       <c r="J399" s="4" t="n">
-        <v>0</v>
+        <v>31.9</v>
       </c>
       <c r="K399" s="4" t="n">
-        <v>0</v>
+        <v>32.13</v>
       </c>
       <c r="L399" s="5">
         <f>F399*(K399-J399)</f>
@@ -14504,29 +14630,29 @@
     <row r="400" ht="16.5" customHeight="1">
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E400" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G400" s="3" t="n">
-        <v>33</v>
+        <v>583</v>
       </c>
       <c r="H400" s="3" t="n">
-        <v>358</v>
+        <v>1084</v>
       </c>
       <c r="I400" s="3" t="n">
-        <v>-325</v>
+        <v>-501</v>
       </c>
       <c r="J400" s="4" t="n">
-        <v>0</v>
+        <v>485.92</v>
       </c>
       <c r="K400" s="4" t="n">
-        <v>0</v>
+        <v>492.59</v>
       </c>
       <c r="L400" s="5">
         <f>F400*(K400-J400)</f>
@@ -14536,29 +14662,29 @@
     <row r="401" ht="16.5" customHeight="1">
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E401" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F401" s="3" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="G401" s="3" t="n">
-        <v>6</v>
+        <v>529</v>
       </c>
       <c r="H401" s="3" t="n">
-        <v>511</v>
+        <v>1501</v>
       </c>
       <c r="I401" s="3" t="n">
-        <v>-505</v>
+        <v>-972</v>
       </c>
       <c r="J401" s="4" t="n">
-        <v>0</v>
+        <v>115.04</v>
       </c>
       <c r="K401" s="4" t="n">
-        <v>0</v>
+        <v>116.35</v>
       </c>
       <c r="L401" s="5">
         <f>F401*(K401-J401)</f>
@@ -14568,29 +14694,29 @@
     <row r="402" ht="16.5" customHeight="1">
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>楠梓電(2316)</t>
         </is>
       </c>
       <c r="E402" s="3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G402" s="3" t="n">
-        <v>3</v>
+        <v>481</v>
       </c>
       <c r="H402" s="3" t="n">
-        <v>610</v>
+        <v>25</v>
       </c>
       <c r="I402" s="3" t="n">
-        <v>-607</v>
+        <v>456</v>
       </c>
       <c r="J402" s="4" t="n">
-        <v>0</v>
+        <v>117.24</v>
       </c>
       <c r="K402" s="4" t="n">
-        <v>0</v>
+        <v>123.5</v>
       </c>
       <c r="L402" s="5">
         <f>F402*(K402-J402)</f>
@@ -14598,59 +14724,164 @@
       </c>
     </row>
     <row r="403" ht="16.5" customHeight="1">
-      <c r="D403" s="2" t="n"/>
-      <c r="E403" s="3" t="n"/>
-      <c r="F403" s="3" t="n"/>
-      <c r="G403" s="3" t="n"/>
-      <c r="H403" s="3" t="n"/>
-      <c r="I403" s="3" t="n"/>
-      <c r="J403" s="4" t="n"/>
-      <c r="K403" s="4" t="n"/>
-      <c r="L403" s="5" t="n"/>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>康舒(6282)</t>
+        </is>
+      </c>
+      <c r="E403" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="F403" s="3" t="n">
+        <v>169</v>
+      </c>
+      <c r="G403" s="3" t="n">
+        <v>380</v>
+      </c>
+      <c r="H403" s="3" t="n">
+        <v>924</v>
+      </c>
+      <c r="I403" s="3" t="n">
+        <v>-544</v>
+      </c>
+      <c r="J403" s="4" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="K403" s="4" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="L403" s="6">
+        <f>F403*(K403-J403)</f>
+        <v/>
+      </c>
     </row>
     <row r="404" ht="16.5" customHeight="1">
-      <c r="D404" s="2" t="n"/>
-      <c r="E404" s="3" t="n"/>
-      <c r="F404" s="3" t="n"/>
-      <c r="G404" s="3" t="n"/>
-      <c r="H404" s="3" t="n"/>
-      <c r="I404" s="3" t="n"/>
-      <c r="J404" s="4" t="n"/>
-      <c r="K404" s="4" t="n"/>
-      <c r="L404" s="5" t="n"/>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>晶豪科(3006)</t>
+        </is>
+      </c>
+      <c r="E404" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F404" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="G404" s="3" t="n">
+        <v>284</v>
+      </c>
+      <c r="H404" s="3" t="n">
+        <v>2816</v>
+      </c>
+      <c r="I404" s="3" t="n">
+        <v>-2532</v>
+      </c>
+      <c r="J404" s="4" t="n">
+        <v>218.69</v>
+      </c>
+      <c r="K404" s="4" t="n">
+        <v>216.63</v>
+      </c>
+      <c r="L404" s="6">
+        <f>F404*(K404-J404)</f>
+        <v/>
+      </c>
     </row>
     <row r="405" ht="16.5" customHeight="1">
-      <c r="D405" s="2" t="n"/>
-      <c r="E405" s="3" t="n"/>
-      <c r="F405" s="3" t="n"/>
-      <c r="G405" s="3" t="n"/>
-      <c r="H405" s="3" t="n"/>
-      <c r="I405" s="3" t="n"/>
-      <c r="J405" s="4" t="n"/>
-      <c r="K405" s="4" t="n"/>
-      <c r="L405" s="5" t="n"/>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>新唐(4919)</t>
+        </is>
+      </c>
+      <c r="E405" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F405" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G405" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="H405" s="3" t="n">
+        <v>658</v>
+      </c>
+      <c r="I405" s="3" t="n">
+        <v>-380</v>
+      </c>
+      <c r="J405" s="4" t="n">
+        <v>185.07</v>
+      </c>
+      <c r="K405" s="4" t="n">
+        <v>182.69</v>
+      </c>
+      <c r="L405" s="6">
+        <f>F405*(K405-J405)</f>
+        <v/>
+      </c>
     </row>
     <row r="406" ht="16.5" customHeight="1">
-      <c r="D406" s="2" t="n"/>
-      <c r="E406" s="3" t="n"/>
-      <c r="F406" s="3" t="n"/>
-      <c r="G406" s="3" t="n"/>
-      <c r="H406" s="3" t="n"/>
-      <c r="I406" s="3" t="n"/>
-      <c r="J406" s="4" t="n"/>
-      <c r="K406" s="4" t="n"/>
-      <c r="L406" s="5" t="n"/>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>健策(3653)</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F406" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G406" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="H406" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="I406" s="3" t="n">
+        <v>-1110</v>
+      </c>
+      <c r="J406" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" s="4" t="n">
+        <v>4135</v>
+      </c>
+      <c r="L406" s="5">
+        <f>F406*(K406-J406)</f>
+        <v/>
+      </c>
     </row>
     <row r="407" ht="16.5" customHeight="1">
-      <c r="D407" s="2" t="n"/>
-      <c r="E407" s="3" t="n"/>
-      <c r="F407" s="3" t="n"/>
-      <c r="G407" s="3" t="n"/>
-      <c r="H407" s="3" t="n"/>
-      <c r="I407" s="3" t="n"/>
-      <c r="J407" s="4" t="n"/>
-      <c r="K407" s="4" t="n"/>
-      <c r="L407" s="5" t="n"/>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>智原(3035)</t>
+        </is>
+      </c>
+      <c r="E407" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F407" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G407" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="H407" s="3" t="n">
+        <v>1696</v>
+      </c>
+      <c r="I407" s="3" t="n">
+        <v>-1578</v>
+      </c>
+      <c r="J407" s="4" t="n">
+        <v>197.33</v>
+      </c>
+      <c r="K407" s="4" t="n">
+        <v>194.93</v>
+      </c>
+      <c r="L407" s="6">
+        <f>F407*(K407-J407)</f>
+        <v/>
+      </c>
     </row>
     <row r="408" ht="16.5" customHeight="1">
       <c r="A408" s="1" t="inlineStr">
@@ -14764,29 +14995,29 @@
     <row r="410" ht="16.5" customHeight="1">
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>閎康(3587)</t>
+          <t>景碩(3189)</t>
         </is>
       </c>
       <c r="E410" s="3" t="n">
-        <v>343</v>
+        <v>491</v>
       </c>
       <c r="F410" s="3" t="n">
-        <v>204</v>
+        <v>30</v>
       </c>
       <c r="G410" s="3" t="n">
-        <v>12022</v>
+        <v>24686</v>
       </c>
       <c r="H410" s="3" t="n">
-        <v>7150</v>
+        <v>1445</v>
       </c>
       <c r="I410" s="3" t="n">
-        <v>4872</v>
+        <v>23241</v>
       </c>
       <c r="J410" s="4" t="n">
-        <v>350.5</v>
+        <v>502.76</v>
       </c>
       <c r="K410" s="4" t="n">
-        <v>350.48</v>
+        <v>481.7</v>
       </c>
       <c r="L410" s="6">
         <f>F410*(K410-J410)</f>
@@ -14796,29 +15027,29 @@
     <row r="411" ht="16.5" customHeight="1">
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>陽程(3498)</t>
+          <t>南亞科(2408)</t>
         </is>
       </c>
       <c r="E411" s="3" t="n">
-        <v>887</v>
+        <v>616</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="G411" s="3" t="n">
-        <v>9092</v>
+        <v>18509</v>
       </c>
       <c r="H411" s="3" t="n">
-        <v>0</v>
+        <v>4643</v>
       </c>
       <c r="I411" s="3" t="n">
-        <v>9092</v>
+        <v>13866</v>
       </c>
       <c r="J411" s="4" t="n">
-        <v>102.5</v>
+        <v>300.47</v>
       </c>
       <c r="K411" s="4" t="n">
-        <v>0</v>
+        <v>301.51</v>
       </c>
       <c r="L411" s="5">
         <f>F411*(K411-J411)</f>
@@ -14828,29 +15059,29 @@
     <row r="412" ht="16.5" customHeight="1">
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>正淩(8147)</t>
+          <t>華邦電(2344)</t>
         </is>
       </c>
       <c r="E412" s="3" t="n">
-        <v>493</v>
+        <v>1265</v>
       </c>
       <c r="F412" s="3" t="n">
-        <v>2</v>
+        <v>270</v>
       </c>
       <c r="G412" s="3" t="n">
-        <v>8356</v>
+        <v>14663</v>
       </c>
       <c r="H412" s="3" t="n">
-        <v>32</v>
+        <v>3110</v>
       </c>
       <c r="I412" s="3" t="n">
-        <v>8324</v>
+        <v>11553</v>
       </c>
       <c r="J412" s="4" t="n">
-        <v>169.5</v>
+        <v>115.91</v>
       </c>
       <c r="K412" s="4" t="n">
-        <v>160</v>
+        <v>115.2</v>
       </c>
       <c r="L412" s="6">
         <f>F412*(K412-J412)</f>
@@ -14860,29 +15091,29 @@
     <row r="413" ht="16.5" customHeight="1">
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>大聯大(3702)</t>
+          <t>閎康(3587)</t>
         </is>
       </c>
       <c r="E413" s="3" t="n">
-        <v>730</v>
+        <v>343</v>
       </c>
       <c r="F413" s="3" t="n">
-        <v>3385</v>
+        <v>204</v>
       </c>
       <c r="G413" s="3" t="n">
-        <v>8345</v>
+        <v>12022</v>
       </c>
       <c r="H413" s="3" t="n">
-        <v>38484</v>
+        <v>7150</v>
       </c>
       <c r="I413" s="3" t="n">
-        <v>-30139</v>
+        <v>4872</v>
       </c>
       <c r="J413" s="4" t="n">
-        <v>114.31</v>
+        <v>350.5</v>
       </c>
       <c r="K413" s="4" t="n">
-        <v>113.69</v>
+        <v>350.48</v>
       </c>
       <c r="L413" s="6">
         <f>F413*(K413-J413)</f>
@@ -14892,29 +15123,29 @@
     <row r="414" ht="16.5" customHeight="1">
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>群創(3481)</t>
         </is>
       </c>
       <c r="E414" s="3" t="n">
-        <v>0</v>
+        <v>3355</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="G414" s="3" t="n">
-        <v>6994</v>
+        <v>10607</v>
       </c>
       <c r="H414" s="3" t="n">
-        <v>642</v>
+        <v>2899</v>
       </c>
       <c r="I414" s="3" t="n">
-        <v>6352</v>
+        <v>7708</v>
       </c>
       <c r="J414" s="4" t="n">
-        <v>0</v>
+        <v>31.62</v>
       </c>
       <c r="K414" s="4" t="n">
-        <v>0</v>
+        <v>32.21</v>
       </c>
       <c r="L414" s="5">
         <f>F414*(K414-J414)</f>
@@ -14924,29 +15155,29 @@
     <row r="415" ht="16.5" customHeight="1">
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>元太(8069)</t>
+          <t>陽程(3498)</t>
         </is>
       </c>
       <c r="E415" s="3" t="n">
-        <v>201</v>
+        <v>887</v>
       </c>
       <c r="F415" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G415" s="3" t="n">
-        <v>3578</v>
+        <v>9092</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I415" s="3" t="n">
-        <v>3418</v>
+        <v>9092</v>
       </c>
       <c r="J415" s="4" t="n">
-        <v>178</v>
+        <v>102.5</v>
       </c>
       <c r="K415" s="4" t="n">
-        <v>178.33</v>
+        <v>0</v>
       </c>
       <c r="L415" s="5">
         <f>F415*(K415-J415)</f>
@@ -14956,29 +15187,29 @@
     <row r="416" ht="16.5" customHeight="1">
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>瑞昱(2379)</t>
+          <t>正淩(8147)</t>
         </is>
       </c>
       <c r="E416" s="3" t="n">
-        <v>56</v>
+        <v>493</v>
       </c>
       <c r="F416" s="3" t="n">
-        <v>464</v>
+        <v>2</v>
       </c>
       <c r="G416" s="3" t="n">
-        <v>3357</v>
+        <v>8356</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>27476</v>
+        <v>32</v>
       </c>
       <c r="I416" s="3" t="n">
-        <v>-24119</v>
+        <v>8324</v>
       </c>
       <c r="J416" s="4" t="n">
-        <v>599.45</v>
+        <v>169.5</v>
       </c>
       <c r="K416" s="4" t="n">
-        <v>592.16</v>
+        <v>160</v>
       </c>
       <c r="L416" s="6">
         <f>F416*(K416-J416)</f>
@@ -14988,29 +15219,29 @@
     <row r="417" ht="16.5" customHeight="1">
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>宜鼎(5289)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E417" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F417" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G417" s="3" t="n">
-        <v>2986</v>
+        <v>6994</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>1624</v>
+        <v>642</v>
       </c>
       <c r="I417" s="3" t="n">
-        <v>1362</v>
+        <v>6352</v>
       </c>
       <c r="J417" s="4" t="n">
-        <v>0</v>
+        <v>2689.92</v>
       </c>
       <c r="K417" s="4" t="n">
-        <v>0</v>
+        <v>3210.5</v>
       </c>
       <c r="L417" s="5">
         <f>F417*(K417-J417)</f>
@@ -15020,31 +15251,31 @@
     <row r="418" ht="16.5" customHeight="1">
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>M31(6643)</t>
+          <t>強茂(2481)</t>
         </is>
       </c>
       <c r="E418" s="3" t="n">
-        <v>0</v>
+        <v>508</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G418" s="3" t="n">
-        <v>2732</v>
+        <v>5533</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="I418" s="3" t="n">
-        <v>2732</v>
+        <v>5295</v>
       </c>
       <c r="J418" s="4" t="n">
-        <v>0</v>
+        <v>108.91</v>
       </c>
       <c r="K418" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L418" s="5">
+        <v>108.09</v>
+      </c>
+      <c r="L418" s="6">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -15119,29 +15350,29 @@
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>國精化(4722)</t>
+          <t>創意(3443)</t>
         </is>
       </c>
       <c r="E420" s="3" t="n">
-        <v>138</v>
+        <v>21</v>
       </c>
       <c r="F420" s="3" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="G420" s="3" t="n">
-        <v>3308</v>
+        <v>11814</v>
       </c>
       <c r="H420" s="3" t="n">
-        <v>1314</v>
+        <v>6136</v>
       </c>
       <c r="I420" s="3" t="n">
-        <v>1994</v>
+        <v>5678</v>
       </c>
       <c r="J420" s="4" t="n">
-        <v>239.73</v>
+        <v>5625.81</v>
       </c>
       <c r="K420" s="4" t="n">
-        <v>238.98</v>
+        <v>5578.64</v>
       </c>
       <c r="L420" s="6">
         <f>F420*(K420-J420)</f>
@@ -15151,29 +15382,29 @@
     <row r="421" ht="16.5" customHeight="1">
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>立隆電(2472)</t>
+          <t>智原(3035)</t>
         </is>
       </c>
       <c r="E421" s="3" t="n">
-        <v>96</v>
+        <v>177</v>
       </c>
       <c r="F421" s="3" t="n">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="G421" s="3" t="n">
-        <v>2149</v>
+        <v>3434</v>
       </c>
       <c r="H421" s="3" t="n">
-        <v>513</v>
+        <v>1792</v>
       </c>
       <c r="I421" s="3" t="n">
-        <v>1636</v>
+        <v>1642</v>
       </c>
       <c r="J421" s="4" t="n">
-        <v>223.83</v>
+        <v>194.04</v>
       </c>
       <c r="K421" s="4" t="n">
-        <v>223.17</v>
+        <v>190.67</v>
       </c>
       <c r="L421" s="6">
         <f>F421*(K421-J421)</f>
@@ -15183,26 +15414,26 @@
     <row r="422" ht="16.5" customHeight="1">
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>藥華藥(6446)</t>
+          <t>世芯-KY(3661)</t>
         </is>
       </c>
       <c r="E422" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F422" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G422" s="3" t="n">
-        <v>1634</v>
+        <v>2663</v>
       </c>
       <c r="H422" s="3" t="n">
-        <v>2546</v>
+        <v>67</v>
       </c>
       <c r="I422" s="3" t="n">
-        <v>-912</v>
+        <v>2596</v>
       </c>
       <c r="J422" s="4" t="n">
-        <v>0</v>
+        <v>5326</v>
       </c>
       <c r="K422" s="4" t="n">
         <v>0</v>
@@ -15215,31 +15446,31 @@
     <row r="423" ht="16.5" customHeight="1">
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>勤誠(8210)</t>
+          <t>康舒(6282)</t>
         </is>
       </c>
       <c r="E423" s="3" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="F423" s="3" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="G423" s="3" t="n">
-        <v>1631</v>
+        <v>2359</v>
       </c>
       <c r="H423" s="3" t="n">
-        <v>3438</v>
+        <v>637</v>
       </c>
       <c r="I423" s="3" t="n">
-        <v>-1807</v>
+        <v>1722</v>
       </c>
       <c r="J423" s="4" t="n">
-        <v>0</v>
+        <v>55.37</v>
       </c>
       <c r="K423" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L423" s="5">
+        <v>54.93</v>
+      </c>
+      <c r="L423" s="6">
         <f>F423*(K423-J423)</f>
         <v/>
       </c>
@@ -15247,31 +15478,31 @@
     <row r="424" ht="16.5" customHeight="1">
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>中美晶(5483)</t>
+          <t>創見(2451)</t>
         </is>
       </c>
       <c r="E424" s="3" t="n">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="F424" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G424" s="3" t="n">
-        <v>1566</v>
+        <v>1786</v>
       </c>
       <c r="H424" s="3" t="n">
-        <v>376</v>
+        <v>860</v>
       </c>
       <c r="I424" s="3" t="n">
-        <v>1190</v>
+        <v>926</v>
       </c>
       <c r="J424" s="4" t="n">
-        <v>161.39</v>
+        <v>343.4</v>
       </c>
       <c r="K424" s="4" t="n">
-        <v>156.46</v>
-      </c>
-      <c r="L424" s="6">
+        <v>343.84</v>
+      </c>
+      <c r="L424" s="5">
         <f>F424*(K424-J424)</f>
         <v/>
       </c>
@@ -15279,29 +15510,29 @@
     <row r="425" ht="16.5" customHeight="1">
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>振樺電(8114)</t>
+          <t>勤誠(8210)</t>
         </is>
       </c>
       <c r="E425" s="3" t="n">
-        <v>61</v>
+        <v>10</v>
       </c>
       <c r="F425" s="3" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="G425" s="3" t="n">
-        <v>1330</v>
+        <v>1631</v>
       </c>
       <c r="H425" s="3" t="n">
-        <v>65</v>
+        <v>3438</v>
       </c>
       <c r="I425" s="3" t="n">
-        <v>1265</v>
+        <v>-1807</v>
       </c>
       <c r="J425" s="4" t="n">
-        <v>218</v>
+        <v>1630.8</v>
       </c>
       <c r="K425" s="4" t="n">
-        <v>216.33</v>
+        <v>1562.77</v>
       </c>
       <c r="L425" s="6">
         <f>F425*(K425-J425)</f>
@@ -15311,29 +15542,29 @@
     <row r="426" ht="16.5" customHeight="1">
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>川湖(2059)</t>
+          <t>中砂(1560)</t>
         </is>
       </c>
       <c r="E426" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G426" s="3" t="n">
-        <v>1289</v>
+        <v>1576</v>
       </c>
       <c r="H426" s="3" t="n">
-        <v>2170</v>
+        <v>126</v>
       </c>
       <c r="I426" s="3" t="n">
-        <v>-881</v>
+        <v>1450</v>
       </c>
       <c r="J426" s="4" t="n">
-        <v>0</v>
+        <v>630.52</v>
       </c>
       <c r="K426" s="4" t="n">
-        <v>0</v>
+        <v>632</v>
       </c>
       <c r="L426" s="5">
         <f>F426*(K426-J426)</f>
@@ -15343,31 +15574,31 @@
     <row r="427" ht="16.5" customHeight="1">
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>譜瑞-KY(4966)</t>
+          <t>中美晶(5483)</t>
         </is>
       </c>
       <c r="E427" s="3" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G427" s="3" t="n">
-        <v>429</v>
+        <v>1566</v>
       </c>
       <c r="H427" s="3" t="n">
-        <v>2742</v>
+        <v>376</v>
       </c>
       <c r="I427" s="3" t="n">
-        <v>-2313</v>
+        <v>1190</v>
       </c>
       <c r="J427" s="4" t="n">
-        <v>0</v>
+        <v>161.39</v>
       </c>
       <c r="K427" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L427" s="5">
+        <v>156.46</v>
+      </c>
+      <c r="L427" s="6">
         <f>F427*(K427-J427)</f>
         <v/>
       </c>
@@ -15375,29 +15606,29 @@
     <row r="428" ht="16.5" customHeight="1">
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>聯詠(3034)</t>
+          <t>志聖(2467)</t>
         </is>
       </c>
       <c r="E428" s="3" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="G428" s="3" t="n">
-        <v>170</v>
+        <v>1352</v>
       </c>
       <c r="H428" s="3" t="n">
-        <v>3166</v>
+        <v>289</v>
       </c>
       <c r="I428" s="3" t="n">
-        <v>-2996</v>
+        <v>1063</v>
       </c>
       <c r="J428" s="4" t="n">
-        <v>565.67</v>
+        <v>588</v>
       </c>
       <c r="K428" s="4" t="n">
-        <v>494.67</v>
+        <v>577.8</v>
       </c>
       <c r="L428" s="6">
         <f>F428*(K428-J428)</f>
@@ -15407,31 +15638,31 @@
     <row r="429" ht="16.5" customHeight="1">
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>大聯大(3702)</t>
+          <t>振樺電(8114)</t>
         </is>
       </c>
       <c r="E429" s="3" t="n">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>215</v>
+        <v>3</v>
       </c>
       <c r="G429" s="3" t="n">
-        <v>138</v>
+        <v>1330</v>
       </c>
       <c r="H429" s="3" t="n">
-        <v>2477</v>
+        <v>65</v>
       </c>
       <c r="I429" s="3" t="n">
-        <v>-2339</v>
+        <v>1265</v>
       </c>
       <c r="J429" s="4" t="n">
-        <v>114.92</v>
+        <v>218</v>
       </c>
       <c r="K429" s="4" t="n">
-        <v>115.21</v>
-      </c>
-      <c r="L429" s="5">
+        <v>216.33</v>
+      </c>
+      <c r="L429" s="6">
         <f>F429*(K429-J429)</f>
         <v/>
       </c>
@@ -15552,10 +15783,10 @@
         </is>
       </c>
       <c r="E432" s="3" t="n">
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G432" s="3" t="n">
         <v>8248</v>
@@ -15567,12 +15798,12 @@
         <v>-1306</v>
       </c>
       <c r="J432" s="4" t="n">
-        <v>0</v>
+        <v>299.91</v>
       </c>
       <c r="K432" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L432" s="5">
+        <v>299.5</v>
+      </c>
+      <c r="L432" s="6">
         <f>F432*(K432-J432)</f>
         <v/>
       </c>
@@ -15616,10 +15847,10 @@
         </is>
       </c>
       <c r="E434" s="3" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="G434" s="3" t="n">
         <v>4248</v>
@@ -15631,12 +15862,12 @@
         <v>-701</v>
       </c>
       <c r="J434" s="4" t="n">
-        <v>0</v>
+        <v>159.69</v>
       </c>
       <c r="K434" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L434" s="5">
+        <v>159.64</v>
+      </c>
+      <c r="L434" s="6">
         <f>F434*(K434-J434)</f>
         <v/>
       </c>
@@ -15680,10 +15911,10 @@
         </is>
       </c>
       <c r="E436" s="3" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G436" s="3" t="n">
         <v>3389</v>
@@ -15695,10 +15926,10 @@
         <v>2153</v>
       </c>
       <c r="J436" s="4" t="n">
-        <v>0</v>
+        <v>677.74</v>
       </c>
       <c r="K436" s="4" t="n">
-        <v>0</v>
+        <v>686.5599999999999</v>
       </c>
       <c r="L436" s="5">
         <f>F436*(K436-J436)</f>
@@ -15712,10 +15943,10 @@
         </is>
       </c>
       <c r="E437" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F437" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G437" s="3" t="n">
         <v>3002</v>
@@ -15727,12 +15958,12 @@
         <v>504</v>
       </c>
       <c r="J437" s="4" t="n">
-        <v>0</v>
+        <v>4288.57</v>
       </c>
       <c r="K437" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L437" s="5">
+        <v>4163.83</v>
+      </c>
+      <c r="L437" s="6">
         <f>F437*(K437-J437)</f>
         <v/>
       </c>
@@ -15744,10 +15975,10 @@
         </is>
       </c>
       <c r="E438" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G438" s="3" t="n">
         <v>2964</v>
@@ -15759,12 +15990,12 @@
         <v>1531</v>
       </c>
       <c r="J438" s="4" t="n">
-        <v>0</v>
+        <v>3705.62</v>
       </c>
       <c r="K438" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L438" s="5">
+        <v>3581.75</v>
+      </c>
+      <c r="L438" s="6">
         <f>F438*(K438-J438)</f>
         <v/>
       </c>
@@ -15776,10 +16007,10 @@
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="G439" s="3" t="n">
         <v>2584</v>
@@ -15791,12 +16022,12 @@
         <v>-707</v>
       </c>
       <c r="J439" s="4" t="n">
-        <v>0</v>
+        <v>527.24</v>
       </c>
       <c r="K439" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L439" s="5">
+        <v>522.41</v>
+      </c>
+      <c r="L439" s="6">
         <f>F439*(K439-J439)</f>
         <v/>
       </c>
@@ -15804,29 +16035,29 @@
     <row r="440" ht="16.5" customHeight="1">
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>奇鋐(3017)</t>
+          <t>元大台灣50正2(00631L)</t>
         </is>
       </c>
       <c r="E440" s="3" t="n">
-        <v>0</v>
+        <v>790</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>0</v>
+        <v>663</v>
       </c>
       <c r="G440" s="3" t="n">
-        <v>2547</v>
+        <v>2580</v>
       </c>
       <c r="H440" s="3" t="n">
-        <v>4151</v>
+        <v>2165</v>
       </c>
       <c r="I440" s="3" t="n">
-        <v>-1604</v>
+        <v>415</v>
       </c>
       <c r="J440" s="4" t="n">
-        <v>0</v>
+        <v>32.66</v>
       </c>
       <c r="K440" s="4" t="n">
-        <v>0</v>
+        <v>32.66</v>
       </c>
       <c r="L440" s="5">
         <f>F440*(K440-J440)</f>
@@ -15981,10 +16212,10 @@
         </is>
       </c>
       <c r="E444" s="3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G444" s="3" t="n">
         <v>5034</v>
@@ -15996,12 +16227,12 @@
         <v>-9278</v>
       </c>
       <c r="J444" s="4" t="n">
-        <v>0</v>
+        <v>3871.92</v>
       </c>
       <c r="K444" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L444" s="5">
+        <v>3868.22</v>
+      </c>
+      <c r="L444" s="6">
         <f>F444*(K444-J444)</f>
         <v/>
       </c>
@@ -16045,10 +16276,10 @@
         </is>
       </c>
       <c r="E446" s="3" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="G446" s="3" t="n">
         <v>3455</v>
@@ -16060,12 +16291,12 @@
         <v>610</v>
       </c>
       <c r="J446" s="4" t="n">
-        <v>0</v>
+        <v>300.42</v>
       </c>
       <c r="K446" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L446" s="5">
+        <v>299.47</v>
+      </c>
+      <c r="L446" s="6">
         <f>F446*(K446-J446)</f>
         <v/>
       </c>
@@ -16141,10 +16372,10 @@
         </is>
       </c>
       <c r="E449" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F449" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G449" s="3" t="n">
         <v>2100</v>
@@ -16156,10 +16387,10 @@
         <v>1552</v>
       </c>
       <c r="J449" s="4" t="n">
-        <v>0</v>
+        <v>5249.75</v>
       </c>
       <c r="K449" s="4" t="n">
-        <v>0</v>
+        <v>5479</v>
       </c>
       <c r="L449" s="5">
         <f>F449*(K449-J449)</f>
@@ -16173,7 +16404,7 @@
         </is>
       </c>
       <c r="E450" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F450" s="3" t="n">
         <v>0</v>
@@ -16188,7 +16419,7 @@
         <v>1483</v>
       </c>
       <c r="J450" s="4" t="n">
-        <v>0</v>
+        <v>4126.25</v>
       </c>
       <c r="K450" s="4" t="n">
         <v>0</v>
@@ -16432,10 +16663,10 @@
         </is>
       </c>
       <c r="E457" s="3" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="F457" s="3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="G457" s="3" t="n">
         <v>3991</v>
@@ -16447,12 +16678,12 @@
         <v>1147</v>
       </c>
       <c r="J457" s="4" t="n">
-        <v>0</v>
+        <v>458.74</v>
       </c>
       <c r="K457" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L457" s="5">
+        <v>458.71</v>
+      </c>
+      <c r="L457" s="6">
         <f>F457*(K457-J457)</f>
         <v/>
       </c>
@@ -16496,10 +16727,10 @@
         </is>
       </c>
       <c r="E459" s="3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F459" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G459" s="3" t="n">
         <v>3489</v>
@@ -16511,10 +16742,10 @@
         <v>1870</v>
       </c>
       <c r="J459" s="4" t="n">
-        <v>0</v>
+        <v>1341.92</v>
       </c>
       <c r="K459" s="4" t="n">
-        <v>0</v>
+        <v>1349.25</v>
       </c>
       <c r="L459" s="5">
         <f>F459*(K459-J459)</f>
@@ -16528,10 +16759,10 @@
         </is>
       </c>
       <c r="E460" s="3" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="F460" s="3" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="G460" s="3" t="n">
         <v>3262</v>
@@ -16543,12 +16774,12 @@
         <v>-2310</v>
       </c>
       <c r="J460" s="4" t="n">
-        <v>0</v>
+        <v>393.06</v>
       </c>
       <c r="K460" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L460" s="5">
+        <v>392.42</v>
+      </c>
+      <c r="L460" s="6">
         <f>F460*(K460-J460)</f>
         <v/>
       </c>
@@ -16592,10 +16823,10 @@
         </is>
       </c>
       <c r="E462" s="3" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F462" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G462" s="3" t="n">
         <v>3158</v>
@@ -16607,10 +16838,10 @@
         <v>1255</v>
       </c>
       <c r="J462" s="4" t="n">
-        <v>0</v>
+        <v>902.26</v>
       </c>
       <c r="K462" s="4" t="n">
-        <v>0</v>
+        <v>906.1</v>
       </c>
       <c r="L462" s="5">
         <f>F462*(K462-J462)</f>

--- a/data/reports/chip_radar_2026-05-11.xlsx
+++ b/data/reports/chip_radar_2026-05-11.xlsx
@@ -1325,7 +1325,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>1613</v>
@@ -1340,9 +1340,9 @@
         <v>2304.43</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="5">
+        <v>226</v>
+      </c>
+      <c r="L24" s="6">
         <f>F24*(K24-J24)</f>
         <v/>
       </c>
@@ -1421,7 +1421,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>1154</v>
@@ -1436,9 +1436,9 @@
         <v>2309</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="5">
+        <v>206</v>
+      </c>
+      <c r="L27" s="6">
         <f>F27*(K27-J27)</f>
         <v/>
       </c>
@@ -1485,7 +1485,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>1071</v>
@@ -1500,9 +1500,9 @@
         <v>5355</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="5">
+        <v>81</v>
+      </c>
+      <c r="L29" s="6">
         <f>F29*(K29-J29)</f>
         <v/>
       </c>
@@ -1549,7 +1549,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>787</v>
@@ -1564,9 +1564,9 @@
         <v>3934.5</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="5">
+        <v>48</v>
+      </c>
+      <c r="L31" s="6">
         <f>F31*(K31-J31)</f>
         <v/>
       </c>
@@ -1581,7 +1581,7 @@
         <v>3</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>780</v>
@@ -1596,9 +1596,9 @@
         <v>2601.67</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="5">
+        <v>26</v>
+      </c>
+      <c r="L32" s="6">
         <f>F32*(K32-J32)</f>
         <v/>
       </c>
@@ -2979,7 +2979,7 @@
         <v>124</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" s="3" t="n">
         <v>33108</v>
@@ -2994,9 +2994,9 @@
         <v>2670</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="5">
+        <v>48</v>
+      </c>
+      <c r="L71" s="6">
         <f>F71*(K71-J71)</f>
         <v/>
       </c>
@@ -3891,7 +3891,7 @@
         <v>3</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="3" t="n">
         <v>1633</v>
@@ -3906,9 +3906,9 @@
         <v>5443.67</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="5">
+        <v>133</v>
+      </c>
+      <c r="L97" s="6">
         <f>F97*(K97-J97)</f>
         <v/>
       </c>
@@ -6482,7 +6482,7 @@
         <v>124</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
         <v>33108</v>
@@ -6497,9 +6497,9 @@
         <v>2670</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L170" s="5">
+        <v>48</v>
+      </c>
+      <c r="L170" s="6">
         <f>F170*(K170-J170)</f>
         <v/>
       </c>
@@ -7256,7 +7256,7 @@
         <v>10</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" s="3" t="n">
         <v>6393</v>
@@ -7271,9 +7271,9 @@
         <v>6392.9</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" s="5">
+        <v>18</v>
+      </c>
+      <c r="L192" s="6">
         <f>F192*(K192-J192)</f>
         <v/>
       </c>
@@ -8072,7 +8072,7 @@
         <v>62</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G215" s="3" t="n">
         <v>13976</v>
@@ -8087,9 +8087,9 @@
         <v>2254.11</v>
       </c>
       <c r="K215" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L215" s="5">
+        <v>740</v>
+      </c>
+      <c r="L215" s="6">
         <f>F215*(K215-J215)</f>
         <v/>
       </c>
@@ -8619,7 +8619,7 @@
         <v>97</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" s="3" t="n">
         <v>2509</v>
@@ -8634,9 +8634,9 @@
         <v>258.66</v>
       </c>
       <c r="K231" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L231" s="5">
+        <v>10</v>
+      </c>
+      <c r="L231" s="6">
         <f>F231*(K231-J231)</f>
         <v/>
       </c>
@@ -8814,7 +8814,7 @@
         <v>10</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" s="3" t="n">
         <v>2826</v>
@@ -8829,9 +8829,9 @@
         <v>2826.4</v>
       </c>
       <c r="K236" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L236" s="5">
+        <v>463</v>
+      </c>
+      <c r="L236" s="6">
         <f>F236*(K236-J236)</f>
         <v/>
       </c>
@@ -11294,7 +11294,7 @@
         <v>3</v>
       </c>
       <c r="F306" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G306" s="3" t="n">
         <v>1633</v>
@@ -11309,9 +11309,9 @@
         <v>5443.67</v>
       </c>
       <c r="K306" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L306" s="5">
+        <v>133</v>
+      </c>
+      <c r="L306" s="6">
         <f>F306*(K306-J306)</f>
         <v/>
       </c>
@@ -13402,7 +13402,7 @@
         <v>38</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G365" s="3" t="n">
         <v>10121</v>
@@ -13417,9 +13417,9 @@
         <v>2663.47</v>
       </c>
       <c r="K365" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L365" s="5">
+        <v>1191</v>
+      </c>
+      <c r="L365" s="6">
         <f>F365*(K365-J365)</f>
         <v/>
       </c>
@@ -14826,7 +14826,7 @@
         </is>
       </c>
       <c r="E406" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F406" s="3" t="n">
         <v>3</v>
@@ -14841,7 +14841,7 @@
         <v>-1110</v>
       </c>
       <c r="J406" s="4" t="n">
-        <v>0</v>
+        <v>1303</v>
       </c>
       <c r="K406" s="4" t="n">
         <v>4135</v>
@@ -15155,29 +15155,29 @@
     <row r="415" ht="16.5" customHeight="1">
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>陽程(3498)</t>
+          <t>蔚華科(3055)</t>
         </is>
       </c>
       <c r="E415" s="3" t="n">
-        <v>887</v>
+        <v>1010</v>
       </c>
       <c r="F415" s="3" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="G415" s="3" t="n">
-        <v>9092</v>
+        <v>10100</v>
       </c>
       <c r="H415" s="3" t="n">
-        <v>0</v>
+        <v>5040</v>
       </c>
       <c r="I415" s="3" t="n">
-        <v>9092</v>
+        <v>5060</v>
       </c>
       <c r="J415" s="4" t="n">
-        <v>102.5</v>
+        <v>100</v>
       </c>
       <c r="K415" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L415" s="5">
         <f>F415*(K415-J415)</f>
@@ -15187,31 +15187,31 @@
     <row r="416" ht="16.5" customHeight="1">
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>正淩(8147)</t>
+          <t>陽程(3498)</t>
         </is>
       </c>
       <c r="E416" s="3" t="n">
-        <v>493</v>
+        <v>887</v>
       </c>
       <c r="F416" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G416" s="3" t="n">
-        <v>8356</v>
+        <v>9092</v>
       </c>
       <c r="H416" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I416" s="3" t="n">
-        <v>8324</v>
+        <v>9092</v>
       </c>
       <c r="J416" s="4" t="n">
-        <v>169.5</v>
+        <v>102.5</v>
       </c>
       <c r="K416" s="4" t="n">
-        <v>160</v>
-      </c>
-      <c r="L416" s="6">
+        <v>0</v>
+      </c>
+      <c r="L416" s="5">
         <f>F416*(K416-J416)</f>
         <v/>
       </c>
@@ -15219,31 +15219,31 @@
     <row r="417" ht="16.5" customHeight="1">
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>群聯(8299)</t>
+          <t>正淩(8147)</t>
         </is>
       </c>
       <c r="E417" s="3" t="n">
-        <v>26</v>
+        <v>493</v>
       </c>
       <c r="F417" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G417" s="3" t="n">
-        <v>6994</v>
+        <v>8356</v>
       </c>
       <c r="H417" s="3" t="n">
-        <v>642</v>
+        <v>32</v>
       </c>
       <c r="I417" s="3" t="n">
-        <v>6352</v>
+        <v>8324</v>
       </c>
       <c r="J417" s="4" t="n">
-        <v>2689.92</v>
+        <v>169.5</v>
       </c>
       <c r="K417" s="4" t="n">
-        <v>3210.5</v>
-      </c>
-      <c r="L417" s="5">
+        <v>160</v>
+      </c>
+      <c r="L417" s="6">
         <f>F417*(K417-J417)</f>
         <v/>
       </c>
@@ -15251,31 +15251,31 @@
     <row r="418" ht="16.5" customHeight="1">
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>強茂(2481)</t>
+          <t>群聯(8299)</t>
         </is>
       </c>
       <c r="E418" s="3" t="n">
-        <v>508</v>
+        <v>26</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="G418" s="3" t="n">
-        <v>5533</v>
+        <v>6994</v>
       </c>
       <c r="H418" s="3" t="n">
-        <v>238</v>
+        <v>642</v>
       </c>
       <c r="I418" s="3" t="n">
-        <v>5295</v>
+        <v>6352</v>
       </c>
       <c r="J418" s="4" t="n">
-        <v>108.91</v>
+        <v>2689.92</v>
       </c>
       <c r="K418" s="4" t="n">
-        <v>108.09</v>
-      </c>
-      <c r="L418" s="6">
+        <v>3210.5</v>
+      </c>
+      <c r="L418" s="5">
         <f>F418*(K418-J418)</f>
         <v/>
       </c>
@@ -15421,7 +15421,7 @@
         <v>5</v>
       </c>
       <c r="F422" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G422" s="3" t="n">
         <v>2663</v>
@@ -15436,9 +15436,9 @@
         <v>5326</v>
       </c>
       <c r="K422" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L422" s="5">
+        <v>672</v>
+      </c>
+      <c r="L422" s="6">
         <f>F422*(K422-J422)</f>
         <v/>
       </c>
@@ -16407,7 +16407,7 @@
         <v>4</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G450" s="3" t="n">
         <v>1650</v>
@@ -16422,9 +16422,9 @@
         <v>4126.25</v>
       </c>
       <c r="K450" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L450" s="5">
+        <v>1672</v>
+      </c>
+      <c r="L450" s="6">
         <f>F450*(K450-J450)</f>
         <v/>
       </c>
